--- a/docs/oc-regiones/articulos-de-aseo-e-higiene/coquimbo.xlsx
+++ b/docs/oc-regiones/articulos-de-aseo-e-higiene/coquimbo.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M377"/>
+  <dimension ref="A1:M380"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>24528.16</v>
+        <v>24402.13</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>1649.97</v>
+        <v>1641.5</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>6240.21</v>
+        <v>6206.1</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>1750.48</v>
+        <v>1740.91</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>3152.54</v>
+        <v>3135.31</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>3077.86</v>
+        <v>3043.56</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>9801.01</v>
+        <v>9747.34</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>9214.040000000001</v>
+        <v>9202.309999999999</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>2254.42</v>
+        <v>2251.55</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>2184.13</v>
+        <v>2181.35</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>969.73</v>
+        <v>968.5</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>1241.76</v>
+        <v>1246.2</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>6634.07</v>
+        <v>6657.74</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>945.83</v>
+        <v>949.21</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>2676.54</v>
+        <v>2705.65</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>2287.62</v>
+        <v>2312.51</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>3548.52</v>
+        <v>3587.11</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>1229.74</v>
+        <v>1243.12</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>3404.99</v>
+        <v>3416.19</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>773.17</v>
+        <v>775.71</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>1776.27</v>
+        <v>1782.11</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>1245.94</v>
+        <v>1267.44</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>3766.07</v>
+        <v>3831.08</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>3331.25</v>
+        <v>3346.76</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>8184.89</v>
+        <v>8170.37</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>2919.9</v>
+        <v>2914.72</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>5532</v>
+        <v>5509.19</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>5769.03</v>
+        <v>5745.25</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>2235.57</v>
+        <v>2226.36</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>2943.79</v>
+        <v>2939.22</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>3436.09</v>
+        <v>3430.77</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>3563.52</v>
+        <v>3581.93</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>2231.59</v>
+        <v>2247.34</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>36858.65</v>
+        <v>37118.78</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>1738.39</v>
+        <v>1750.66</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>4550.38</v>
+        <v>4491.57</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>6006.3</v>
+        <v>5930.01</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>26809.42</v>
+        <v>26468.88</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>6102.37</v>
+        <v>6024.85</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>3024.77</v>
+        <v>2994.67</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>3426.23</v>
+        <v>3392.14</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>2516.02</v>
+        <v>2490.99</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>14653.65</v>
+        <v>14507.85</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>778.54</v>
+        <v>775.75</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>6360.34</v>
+        <v>6333.68</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>3722.11</v>
+        <v>3679.03</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>2180.07</v>
+        <v>2154.84</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>3241.48</v>
+        <v>3203.97</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>967.34</v>
+        <v>959.15</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>2805.75</v>
+        <v>2781.98</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>807.89</v>
+        <v>801.04</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>5279.57</v>
+        <v>5234.84</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>1140.71</v>
+        <v>1139.79</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>6026.16</v>
+        <v>6021.32</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>1186.8</v>
+        <v>1191.35</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>3883.94</v>
+        <v>3901.55</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>2869.44</v>
+        <v>2882.45</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>5690.6</v>
+        <v>5729.77</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>8550.58</v>
+        <v>8609.43</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>6226.56</v>
+        <v>6279.77</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>1079.38</v>
+        <v>1088.61</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>3623.92</v>
+        <v>3662.79</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>1864.56</v>
+        <v>1884.56</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>3804.72</v>
+        <v>3845.54</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>2286.8</v>
+        <v>2299.3</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>5775.63</v>
+        <v>5807.22</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>1715.76</v>
+        <v>1682.3</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>3262.76</v>
+        <v>3221.34</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>1102.81</v>
+        <v>1086.92</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>8921.67</v>
+        <v>8806.360000000001</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>5134.19</v>
+        <v>5067.84</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>3952.33</v>
+        <v>3944.54</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>7196.54</v>
+        <v>7182.36</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>2834.04</v>
+        <v>2837.97</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>1552.85</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>9853.25</v>
+        <v>9866.93</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>1164.71</v>
+        <v>1166.32</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>6209.78</v>
+        <v>6205.54</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>2127.72</v>
+        <v>2126.27</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>2505.96</v>
+        <v>2497.36</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>2601.04</v>
+        <v>2592.12</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>1138.73</v>
+        <v>1132.71</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>8624.07</v>
+        <v>8578.51</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>2095.95</v>
+        <v>2082.81</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>4610.87</v>
+        <v>4681.06</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>28661.67</v>
+        <v>29358.66</v>
       </c>
     </row>
     <row r="88">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>2002.06</v>
+        <v>2052.68</v>
       </c>
     </row>
     <row r="89">
@@ -5876,13 +5876,13 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>2082.58</v>
+        <v>2135.23</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2555-4-CM26</t>
+          <t>1057439-697-CM26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5907,12 +5907,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.606.402-9</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>GRUPO NUVIX SPA</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>78.209.441-6</t>
         </is>
       </c>
       <c r="K90" t="inlineStr"/>
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>2408.91</v>
+        <v>4505.06</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>7003.37</v>
+        <v>7215.74</v>
       </c>
     </row>
     <row r="92">
@@ -6059,13 +6059,13 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>2687.94</v>
+        <v>2769.45</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1057439-697-CM26</t>
+          <t>2555-4-CM26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6090,12 +6090,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>61.606.402-9</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6105,12 +6105,12 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>GRUPO NUVIX SPA</t>
+          <t>Comercial Agustin Limitada</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>78.209.441-6</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K93" t="inlineStr"/>
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>4372.48</v>
+        <v>2481.95</v>
       </c>
     </row>
     <row r="94">
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>2728.04</v>
+        <v>2810.77</v>
       </c>
     </row>
     <row r="95">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>1860.19</v>
+        <v>1916.59</v>
       </c>
     </row>
     <row r="96">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>3108.26</v>
+        <v>3202.51</v>
       </c>
     </row>
     <row r="97">
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>6245.48</v>
+        <v>6434.86</v>
       </c>
     </row>
     <row r="98">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>3581.99</v>
+        <v>3688.45</v>
       </c>
     </row>
     <row r="99">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>19939.3</v>
+        <v>20531.95</v>
       </c>
     </row>
     <row r="100">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>878.26</v>
+        <v>904.37</v>
       </c>
     </row>
     <row r="101">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>36127.13</v>
+        <v>35998.51</v>
       </c>
     </row>
     <row r="102">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>810.51</v>
+        <v>807.63</v>
       </c>
     </row>
     <row r="103">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>1775.46</v>
+        <v>1769.14</v>
       </c>
     </row>
     <row r="104">
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>13167.11</v>
+        <v>13205.25</v>
       </c>
     </row>
     <row r="105">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>1528.95</v>
+        <v>1533.38</v>
       </c>
     </row>
     <row r="106">
@@ -6913,7 +6913,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>1306.85</v>
+        <v>1313.61</v>
       </c>
     </row>
     <row r="107">
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>7274.79</v>
+        <v>7312.37</v>
       </c>
     </row>
     <row r="108">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>18011.25</v>
+        <v>18104.29</v>
       </c>
     </row>
     <row r="109">
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>815.71</v>
+        <v>819.92</v>
       </c>
     </row>
     <row r="110">
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>5180.21</v>
+        <v>5206.97</v>
       </c>
     </row>
     <row r="111">
@@ -7218,7 +7218,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>4843.9</v>
+        <v>4868.92</v>
       </c>
     </row>
     <row r="112">
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>2188.39</v>
+        <v>2199.69</v>
       </c>
     </row>
     <row r="113">
@@ -7340,7 +7340,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>1050.65</v>
+        <v>1056.08</v>
       </c>
     </row>
     <row r="114">
@@ -7401,7 +7401,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>2761.52</v>
+        <v>2749.88</v>
       </c>
     </row>
     <row r="115">
@@ -7462,7 +7462,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>1318.94</v>
+        <v>1313.38</v>
       </c>
     </row>
     <row r="116">
@@ -7523,13 +7523,13 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>3604.71</v>
+        <v>3589.51</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>3614-10-CM26</t>
+          <t>3614-9-CM26</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K117" t="inlineStr"/>
@@ -7584,13 +7584,13 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>5915.66</v>
+        <v>3995.73</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>1984-2-CM26</t>
+          <t>3614-10-CM26</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>60.701.009-9</t>
+          <t>69.040.500-8</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Pesca y Acuicultura</t>
+          <t>I MUNICIPALIDAD DE VICUNA</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7630,12 +7630,12 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>76.475.342-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K118" t="inlineStr"/>
@@ -7645,13 +7645,13 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>2829.5</v>
+        <v>5931.9</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>3614-9-CM26</t>
+          <t>1984-2-CM26</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7676,12 +7676,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>69.040.500-8</t>
+          <t>60.701.009-9</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VICUNA</t>
+          <t>Servicio Nacional de Pesca y Acuicultura</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>EQUILIBRIUM SPA</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.475.342-9</t>
         </is>
       </c>
       <c r="K119" t="inlineStr"/>
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>3984.8</v>
+        <v>2837.26</v>
       </c>
     </row>
     <row r="120">
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>6767.39</v>
+        <v>6828.94</v>
       </c>
     </row>
     <row r="121">
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>41866.11</v>
+        <v>42246.91</v>
       </c>
     </row>
     <row r="122">
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>30058.62</v>
+        <v>30332.03</v>
       </c>
     </row>
     <row r="123">
@@ -7950,7 +7950,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>1140.81</v>
+        <v>1151.19</v>
       </c>
     </row>
     <row r="124">
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>2922.2</v>
+        <v>2942.54</v>
       </c>
     </row>
     <row r="125">
@@ -8072,7 +8072,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>2706.08</v>
+        <v>2724.92</v>
       </c>
     </row>
     <row r="126">
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>4009.97</v>
+        <v>4037.89</v>
       </c>
     </row>
     <row r="127">
@@ -8194,7 +8194,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>11957.07</v>
+        <v>12040.32</v>
       </c>
     </row>
     <row r="128">
@@ -8255,13 +8255,13 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>1220.2</v>
+        <v>1228.69</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>3714-19-CM26</t>
+          <t>1057439-1093-CM26</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8286,12 +8286,12 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>61.606.402-9</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>GRUPO NUVIX SPA</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>78.209.441-6</t>
         </is>
       </c>
       <c r="K129" t="inlineStr"/>
@@ -8316,13 +8316,13 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>7936.21</v>
+        <v>12456.11</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>1057439-1093-CM26</t>
+          <t>1057439-1074-CM26</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8377,13 +8377,13 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>12374.61</v>
+        <v>2076.02</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>1057439-1074-CM26</t>
+          <t>3714-19-CM26</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8408,12 +8408,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>61.606.402-9</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>GRUPO NUVIX SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>78.209.441-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K131" t="inlineStr"/>
@@ -8438,7 +8438,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>2062.43</v>
+        <v>7988.48</v>
       </c>
     </row>
     <row r="132">
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>2706.08</v>
+        <v>2723.9</v>
       </c>
     </row>
     <row r="133">
@@ -8560,7 +8560,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>2185.54</v>
+        <v>2199.93</v>
       </c>
     </row>
     <row r="134">
@@ -8621,7 +8621,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>34041.21</v>
+        <v>33982.87</v>
       </c>
     </row>
     <row r="135">
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>8144.67</v>
+        <v>8130.71</v>
       </c>
     </row>
     <row r="136">
@@ -8743,7 +8743,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>39018.12</v>
+        <v>38951.24</v>
       </c>
     </row>
     <row r="137">
@@ -8804,7 +8804,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>12369.44</v>
+        <v>12356.68</v>
       </c>
     </row>
     <row r="138">
@@ -8865,7 +8865,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>1516.74</v>
+        <v>1505.87</v>
       </c>
     </row>
     <row r="139">
@@ -8926,7 +8926,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>1676.44</v>
+        <v>1664.43</v>
       </c>
     </row>
     <row r="140">
@@ -8987,7 +8987,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>1739.45</v>
+        <v>1736.89</v>
       </c>
     </row>
     <row r="141">
@@ -9048,13 +9048,13 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>829.03</v>
+        <v>824.52</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2710-63-CM26</t>
+          <t>1673-42-CM26</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9074,17 +9074,17 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>69.040.700-0</t>
+          <t>61.606.401-0</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE OVALLE</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL VICUNA</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -9094,12 +9094,12 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>Comercial Agustin Limitada</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K142" t="inlineStr"/>
@@ -9109,13 +9109,13 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>2720.09</v>
+        <v>4280.12</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>1673-42-CM26</t>
+          <t>2710-63-CM26</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9135,17 +9135,17 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>61.606.401-0</t>
+          <t>69.040.700-0</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL VICUNA</t>
+          <t>MUNICIPALIDAD DE OVALLE</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -9155,12 +9155,12 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K143" t="inlineStr"/>
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>4303.56</v>
+        <v>2705.28</v>
       </c>
     </row>
     <row r="144">
@@ -9231,7 +9231,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>2656.91</v>
+        <v>2646.66</v>
       </c>
     </row>
     <row r="145">
@@ -9292,7 +9292,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>9806.83</v>
+        <v>9768.98</v>
       </c>
     </row>
     <row r="146">
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>11705.08</v>
+        <v>11659.9</v>
       </c>
     </row>
     <row r="147">
@@ -9414,7 +9414,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>2427.51</v>
+        <v>2418.14</v>
       </c>
     </row>
     <row r="148">
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>8405.469999999999</v>
+        <v>8448.99</v>
       </c>
     </row>
     <row r="149">
@@ -9536,7 +9536,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>2589.08</v>
+        <v>2602.48</v>
       </c>
     </row>
     <row r="150">
@@ -9597,7 +9597,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>2640.77</v>
+        <v>2654.44</v>
       </c>
     </row>
     <row r="151">
@@ -9658,13 +9658,13 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>3718.4</v>
+        <v>3737.65</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>1242121-117-CM26</t>
+          <t>1242121-116-CM26</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -9704,12 +9704,12 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>Comercial Agustin Limitada</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K152" t="inlineStr"/>
@@ -9719,13 +9719,13 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>1717.96</v>
+        <v>5792.16</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>1242121-118-CM26</t>
+          <t>1242121-117-CM26</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -9765,12 +9765,12 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K153" t="inlineStr"/>
@@ -9780,13 +9780,13 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>1803.57</v>
+        <v>1719.62</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>1242121-116-CM26</t>
+          <t>1242121-118-CM26</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -9826,12 +9826,12 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K154" t="inlineStr"/>
@@ -9841,13 +9841,13 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>5786.58</v>
+        <v>1805.31</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>1395-45-CM26</t>
+          <t>5416-77-CM26</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -9872,12 +9872,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>61.606.400-2</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -9902,13 +9902,13 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>11350.4</v>
+        <v>6463.67</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>3714-32-CM26</t>
+          <t>2146-78-CM26</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -9933,12 +9933,12 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>61.606.405-3</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE ANDACOLLO</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -9948,12 +9948,12 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K156" t="inlineStr"/>
@@ -9963,13 +9963,13 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>3227.65</v>
+        <v>3510.08</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>1079505-56-CM26</t>
+          <t>1395-45-CM26</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -9994,12 +9994,12 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>61.606.400-2</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>SERVICIO DE SALUD COQUIMBO</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -10009,12 +10009,12 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>MALMO S.A.</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>76.195.558-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K157" t="inlineStr"/>
@@ -10024,13 +10024,13 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>989.5599999999999</v>
+        <v>11851.66</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2146-78-CM26</t>
+          <t>3714-32-CM26</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10055,12 +10055,12 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>61.606.405-3</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE ANDACOLLO</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -10070,12 +10070,12 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K158" t="inlineStr"/>
@@ -10085,13 +10085,13 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>3361.62</v>
+        <v>3370.19</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>5416-77-CM26</t>
+          <t>1079505-56-CM26</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10116,12 +10116,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>SECCIÓN COMPRAS IV ZONA</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10131,12 +10131,12 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>MALMO S.A.</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.195.558-6</t>
         </is>
       </c>
       <c r="K159" t="inlineStr"/>
@@ -10146,7 +10146,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>6190.3</v>
+        <v>1033.26</v>
       </c>
     </row>
     <row r="160">
@@ -10207,7 +10207,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>3631.63</v>
+        <v>3737.11</v>
       </c>
     </row>
     <row r="161">
@@ -10268,7 +10268,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>1753.82</v>
+        <v>1804.76</v>
       </c>
     </row>
     <row r="162">
@@ -10329,7 +10329,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>3236.74</v>
+        <v>3249.5</v>
       </c>
     </row>
     <row r="163">
@@ -10390,7 +10390,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>3418.38</v>
+        <v>3431.86</v>
       </c>
     </row>
     <row r="164">
@@ -10451,13 +10451,13 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>2204.3</v>
+        <v>2240.63</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>1057438-54-CM26</t>
+          <t>5553-10-CM26</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -10482,12 +10482,12 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>61.606.401-0</t>
+          <t>61.533.000-0</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL VICUNA</t>
+          <t>INSTITUTO DE SEGURIDAD LABORAL</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -10497,12 +10497,12 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>EQUILIBRIUM SPA</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>76.475.342-9</t>
         </is>
       </c>
       <c r="K165" t="inlineStr"/>
@@ -10512,13 +10512,13 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>2786.5</v>
+        <v>1768.99</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>5553-10-CM26</t>
+          <t>1057438-54-CM26</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -10543,12 +10543,12 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>61.533.000-0</t>
+          <t>61.606.401-0</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>INSTITUTO DE SEGURIDAD LABORAL</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL VICUNA</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -10558,12 +10558,12 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM SPA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>76.475.342-9</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K166" t="inlineStr"/>
@@ -10573,13 +10573,13 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>1740.31</v>
+        <v>2832.42</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>3260-17-CM26</t>
+          <t>5416-99-CM26</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -10599,17 +10599,17 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>69.041.000-1</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RIO HURTADO</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -10619,12 +10619,12 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K167" t="inlineStr"/>
@@ -10634,13 +10634,13 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>2391</v>
+        <v>2084.07</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>5416-92-CM26</t>
+          <t>3260-17-CM26</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -10660,17 +10660,17 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>69.041.000-1</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>I MUNICIPALIDAD DE RIO HURTADO</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -10695,13 +10695,13 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>5394.92</v>
+        <v>2396.89</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>5416-99-CM26</t>
+          <t>5416-92-CM26</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -10741,12 +10741,12 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K169" t="inlineStr"/>
@@ -10756,7 +10756,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>2078.95</v>
+        <v>5408.19</v>
       </c>
     </row>
     <row r="170">
@@ -10817,7 +10817,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>3256.94</v>
+        <v>3215.01</v>
       </c>
     </row>
     <row r="171">
@@ -10878,7 +10878,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>5119.26</v>
+        <v>5083.14</v>
       </c>
     </row>
     <row r="172">
@@ -10939,7 +10939,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>1542.27</v>
+        <v>1531.39</v>
       </c>
     </row>
     <row r="173">
@@ -11000,7 +11000,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>5978.88</v>
+        <v>6087.28</v>
       </c>
     </row>
     <row r="174">
@@ -11061,7 +11061,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>3646.24</v>
+        <v>3712.34</v>
       </c>
     </row>
     <row r="175">
@@ -11122,13 +11122,13 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>3302.49</v>
+        <v>3354.23</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>1229788-59-CM26</t>
+          <t>527481-28-CM26</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11148,17 +11148,17 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>61.606.400-2</t>
+          <t>69.041.100-8</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Servicio de Salud Coquimbo</t>
+          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>EQUILIBRIUM SPA</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>76.475.342-9</t>
         </is>
       </c>
       <c r="K176" t="inlineStr"/>
@@ -11183,13 +11183,13 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>11162.44</v>
+        <v>7871.06</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>527481-28-CM26</t>
+          <t>1229788-59-CM26</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11209,17 +11209,17 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>69.041.100-8</t>
+          <t>61.606.400-2</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
+          <t>Servicio de Salud Coquimbo</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -11229,12 +11229,12 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM SPA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>76.475.342-9</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K177" t="inlineStr"/>
@@ -11244,7 +11244,7 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>7749.67</v>
+        <v>11337.3</v>
       </c>
     </row>
     <row r="178">
@@ -11305,7 +11305,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>23447.06</v>
+        <v>23445.85</v>
       </c>
     </row>
     <row r="179">
@@ -11366,7 +11366,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>6577.75</v>
+        <v>6548.34</v>
       </c>
     </row>
     <row r="180">
@@ -11427,7 +11427,7 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>4448.75</v>
+        <v>4428.86</v>
       </c>
     </row>
     <row r="181">
@@ -11488,7 +11488,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>1403.06</v>
+        <v>1404.27</v>
       </c>
     </row>
     <row r="182">
@@ -11549,7 +11549,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>11371.49</v>
+        <v>11381.29</v>
       </c>
     </row>
     <row r="183">
@@ -11610,7 +11610,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>6267.94</v>
+        <v>6273.34</v>
       </c>
     </row>
     <row r="184">
@@ -11671,7 +11671,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>2260.44</v>
+        <v>2262.39</v>
       </c>
     </row>
     <row r="185">
@@ -11732,7 +11732,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>1511.45</v>
+        <v>1512.75</v>
       </c>
     </row>
     <row r="186">
@@ -11793,7 +11793,7 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>2198.09</v>
+        <v>2207.17</v>
       </c>
     </row>
     <row r="187">
@@ -11854,13 +11854,13 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>1106.16</v>
+        <v>1103.11</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>1242121-146-CM26</t>
+          <t>1230663-47-CM26</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -11885,12 +11885,12 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>61.606.404-5</t>
+          <t>65.100.165-k</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Servicio de Salud Coquimbo Hospital de Ovalle</t>
+          <t>CORPORACION CULTURAL MUNICIPAL DE VICUNA</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -11900,12 +11900,12 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K188" t="inlineStr"/>
@@ -11915,13 +11915,13 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>2176.19</v>
+        <v>889.96</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>1230663-47-CM26</t>
+          <t>1242121-146-CM26</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -11946,12 +11946,12 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>65.100.165-k</t>
+          <t>61.606.404-5</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>CORPORACION CULTURAL MUNICIPAL DE VICUNA</t>
+          <t>Servicio de Salud Coquimbo Hospital de Ovalle</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -11961,12 +11961,12 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>Comercial Agustin Limitada</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K189" t="inlineStr"/>
@@ -11976,7 +11976,7 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>900.35</v>
+        <v>2151.07</v>
       </c>
     </row>
     <row r="190">
@@ -12037,13 +12037,13 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>819.1799999999999</v>
+        <v>809.73</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>3511-71-CM26</t>
+          <t>5416-176-CM26</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12063,17 +12063,17 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -12083,12 +12083,12 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA  M&amp;A SPA</t>
+          <t>ROLAND VORWERK Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>77.577.274-3</t>
+          <t>78.178.530-k</t>
         </is>
       </c>
       <c r="K191" t="inlineStr"/>
@@ -12098,13 +12098,13 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>1322.9</v>
+        <v>2195.95</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>5416-173-CM26</t>
+          <t>3511-71-CM26</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -12124,17 +12124,17 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIALIZADORA  M&amp;A SPA</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.577.274-3</t>
         </is>
       </c>
       <c r="K192" t="inlineStr"/>
@@ -12159,13 +12159,13 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>3553.63</v>
+        <v>1303.17</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>5416-176-CM26</t>
+          <t>5416-173-CM26</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12205,12 +12205,12 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>ROLAND VORWERK Y COMPANIA LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>78.178.530-k</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K193" t="inlineStr"/>
@@ -12220,7 +12220,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>2229.2</v>
+        <v>3500.62</v>
       </c>
     </row>
     <row r="194">
@@ -12281,7 +12281,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>770.47</v>
+        <v>766.04</v>
       </c>
     </row>
     <row r="195">
@@ -12342,7 +12342,7 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>2618.25</v>
+        <v>2603.21</v>
       </c>
     </row>
     <row r="196">
@@ -12403,7 +12403,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>2209.88</v>
+        <v>2197.19</v>
       </c>
     </row>
     <row r="197">
@@ -12464,7 +12464,7 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>1989.26</v>
+        <v>1980.69</v>
       </c>
     </row>
     <row r="198">
@@ -12525,7 +12525,7 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>37365.34</v>
+        <v>37204.37</v>
       </c>
     </row>
     <row r="199">
@@ -12586,13 +12586,13 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>9527.129999999999</v>
+        <v>9486.09</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2125-706-CM26</t>
+          <t>1057438-63-CM26</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -12617,12 +12617,12 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>61.606.407-k</t>
+          <t>61.606.401-0</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DR. HUMBERTO ELORZA CORTES</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL VICUNA</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -12632,12 +12632,12 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DEEP FLY S.A</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.419.925-1</t>
         </is>
       </c>
       <c r="K200" t="inlineStr"/>
@@ -12647,13 +12647,13 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>1236.46</v>
+        <v>764.01</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>1057438-63-CM26</t>
+          <t>2125-706-CM26</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -12678,12 +12678,12 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>61.606.401-0</t>
+          <t>61.606.407-k</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL VICUNA</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DR. HUMBERTO ELORZA CORTES</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -12693,12 +12693,12 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>DEEP FLY S.A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>76.419.925-1</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K201" t="inlineStr"/>
@@ -12708,7 +12708,7 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>780.8099999999999</v>
+        <v>1209.86</v>
       </c>
     </row>
     <row r="202">
@@ -12769,13 +12769,13 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>1151.95</v>
+        <v>1125.15</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>1660-219-CM26</t>
+          <t>548238-27-CM26</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -12795,17 +12795,17 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>61.606.408-8</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD COQUIMBO HOSP DE SALAMANC</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -12815,12 +12815,12 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K203" t="inlineStr"/>
@@ -12830,13 +12830,13 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>8226.65</v>
+        <v>2082.48</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>548238-27-CM26</t>
+          <t>1660-219-CM26</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -12856,17 +12856,17 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>61.606.408-8</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>SERVICIO SALUD COQUIMBO HOSP DE SALAMANC</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -12876,12 +12876,12 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K204" t="inlineStr"/>
@@ -12891,7 +12891,7 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>2151.07</v>
+        <v>7964.33</v>
       </c>
     </row>
     <row r="205">
@@ -12952,7 +12952,7 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>3120.71</v>
+        <v>3038.53</v>
       </c>
     </row>
     <row r="206">
@@ -13013,7 +13013,7 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>5148.82</v>
+        <v>5010.96</v>
       </c>
     </row>
     <row r="207">
@@ -13074,7 +13074,7 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>1936.53</v>
+        <v>1884.67</v>
       </c>
     </row>
     <row r="208">
@@ -13135,7 +13135,7 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>5485.3</v>
+        <v>5338.42</v>
       </c>
     </row>
     <row r="209">
@@ -13196,7 +13196,7 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>783.46</v>
+        <v>762.48</v>
       </c>
     </row>
     <row r="210">
@@ -13257,13 +13257,13 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>8694.450000000001</v>
+        <v>8461.639999999999</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>1660-245-CM26</t>
+          <t>3712-270-CM26</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -13288,12 +13288,12 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>61.606.408-8</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD COQUIMBO HOSP DE SALAMANC</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -13318,13 +13318,13 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>1114.28</v>
+        <v>8774.67</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>3712-270-CM26</t>
+          <t>1660-245-CM26</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -13349,12 +13349,12 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>61.606.408-8</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>SERVICIO SALUD COQUIMBO HOSP DE SALAMANC</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -13379,7 +13379,7 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>8749.200000000001</v>
+        <v>1117.52</v>
       </c>
     </row>
     <row r="213">
@@ -13440,13 +13440,13 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>3753.35</v>
+        <v>3768.95</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>1057439-2415-CM26</t>
+          <t>2125-819-CM26</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -13471,12 +13471,12 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>61.606.402-9</t>
+          <t>61.606.407-k</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DR. HUMBERTO ELORZA CORTES</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -13486,12 +13486,12 @@
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>GRUPO NUVIX SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>78.209.441-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K214" t="inlineStr"/>
@@ -13501,13 +13501,13 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>3123.55</v>
+        <v>1487.26</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2125-819-CM26</t>
+          <t>1057439-2415-CM26</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -13532,12 +13532,12 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>61.606.407-k</t>
+          <t>61.606.402-9</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DR. HUMBERTO ELORZA CORTES</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -13547,12 +13547,12 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>GRUPO NUVIX SPA</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>78.209.441-6</t>
         </is>
       </c>
       <c r="K215" t="inlineStr"/>
@@ -13562,7 +13562,7 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>1474.75</v>
+        <v>3150.06</v>
       </c>
     </row>
     <row r="216">
@@ -13623,7 +13623,7 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>2783.91</v>
+        <v>2779.26</v>
       </c>
     </row>
     <row r="217">
@@ -13684,7 +13684,7 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>934.13</v>
+        <v>932.5700000000001</v>
       </c>
     </row>
     <row r="218">
@@ -13745,7 +13745,7 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>2261.27</v>
+        <v>2289.1</v>
       </c>
     </row>
     <row r="219">
@@ -13806,7 +13806,7 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>2021.6</v>
+        <v>2046.48</v>
       </c>
     </row>
     <row r="220">
@@ -13867,13 +13867,13 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>2100.44</v>
+        <v>2126.29</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2996-86-CM26</t>
+          <t>2711-94-CM26</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -13893,17 +13893,17 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>69.040.800-7</t>
+          <t>69.040.700-0</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
+          <t>MUNICIPALIDAD DE OVALLE</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -13913,12 +13913,12 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K221" t="inlineStr"/>
@@ -13928,7 +13928,7 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>2770.86</v>
+        <v>1248.88</v>
       </c>
     </row>
     <row r="222">
@@ -13989,7 +13989,7 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>8601.75</v>
+        <v>8716.26</v>
       </c>
     </row>
     <row r="223">
@@ -14050,13 +14050,13 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>1039.73</v>
+        <v>1053.57</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>2711-94-CM26</t>
+          <t>2711-93-CM26</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -14096,12 +14096,12 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K224" t="inlineStr"/>
@@ -14111,13 +14111,13 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>1232.48</v>
+        <v>1733.62</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>2996-84-CM26</t>
+          <t>2996-86-CM26</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -14157,12 +14157,12 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>Comercial Agustin Limitada</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K225" t="inlineStr"/>
@@ -14172,13 +14172,13 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>3029.03</v>
+        <v>2807.75</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>2711-92-CM26</t>
+          <t>2996-84-CM26</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -14198,17 +14198,17 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>69.040.700-0</t>
+          <t>69.040.800-7</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE OVALLE</t>
+          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -14218,12 +14218,12 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K226" t="inlineStr"/>
@@ -14233,7 +14233,7 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>2588.73</v>
+        <v>3069.36</v>
       </c>
     </row>
     <row r="227">
@@ -14294,13 +14294,13 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>784.6</v>
+        <v>795.04</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>2711-93-CM26</t>
+          <t>2711-92-CM26</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -14340,12 +14340,12 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>Comercial Agustin Limitada</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K228" t="inlineStr"/>
@@ -14355,13 +14355,13 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>1710.85</v>
+        <v>2623.2</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>3873-8391-CM26</t>
+          <t>2146-165-CM26</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -14381,17 +14381,17 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>69.040.900-3</t>
+          <t>61.606.405-3</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUNITAQUI</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE ANDACOLLO</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -14401,12 +14401,12 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K229" t="inlineStr"/>
@@ -14416,13 +14416,13 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>1264.69</v>
+        <v>1651.44</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>2146-165-CM26</t>
+          <t>2996-90-CM26</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -14447,12 +14447,12 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>61.606.405-3</t>
+          <t>69.040.800-7</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE ANDACOLLO</t>
+          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -14477,13 +14477,13 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>1630.16</v>
+        <v>4108.29</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>2996-90-CM26</t>
+          <t>3873-8391-CM26</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -14503,17 +14503,17 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>69.040.800-7</t>
+          <t>69.040.900-3</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
+          <t>I MUNICIPALIDAD DE PUNITAQUI</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -14523,12 +14523,12 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K231" t="inlineStr"/>
@@ -14538,7 +14538,7 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>4055.37</v>
+        <v>1281.19</v>
       </c>
     </row>
     <row r="232">
@@ -14599,13 +14599,13 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>7075.04</v>
+        <v>7167.36</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>1962-192-CM26</t>
+          <t>2288-328-CM26</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -14630,12 +14630,12 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>61.004.012-8</t>
+          <t>69.041.300-0</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Gendarmería de Chile - Dirección Regional de Coquimbo</t>
+          <t>I MUNICIPALIDAD DE CANELA</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -14645,12 +14645,12 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K233" t="inlineStr"/>
@@ -14660,13 +14660,13 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>930.6</v>
+        <v>825.73</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>2288-328-CM26</t>
+          <t>1962-192-CM26</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -14691,12 +14691,12 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>69.041.300-0</t>
+          <t>61.004.012-8</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CANELA</t>
+          <t>Gendarmería de Chile - Dirección Regional de Coquimbo</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -14706,12 +14706,12 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K234" t="inlineStr"/>
@@ -14721,13 +14721,13 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>805.9</v>
+        <v>953.5</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>2450-474-CM26</t>
+          <t>3597-272-CM26</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -14747,17 +14747,17 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>69.040.100-2</t>
+          <t>69.040.500-8</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA SERENA</t>
+          <t>I MUNICIPALIDAD DE VICUNA</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -14767,12 +14767,12 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>MAKRON CHILE SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>78.209.499-8</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K235" t="inlineStr"/>
@@ -14782,13 +14782,13 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>38412.66</v>
+        <v>11696.43</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>3597-272-CM26</t>
+          <t>2450-474-CM26</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -14808,17 +14808,17 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>69.040.500-8</t>
+          <t>69.040.100-2</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VICUNA</t>
+          <t>I MUNICIPALIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -14828,12 +14828,12 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>MAKRON CHILE SPA</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>78.209.499-8</t>
         </is>
       </c>
       <c r="K236" t="inlineStr"/>
@@ -14843,13 +14843,13 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>11479.32</v>
+        <v>39139.15</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>3714-105-CM26</t>
+          <t>646-39-CM26</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -14874,12 +14874,12 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>61.816.000-9</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION IV REGION</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -14889,12 +14889,12 @@
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.008.207-2</t>
         </is>
       </c>
       <c r="K237" t="inlineStr"/>
@@ -14904,13 +14904,13 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>1913.34</v>
+        <v>1466.94</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>3714-106-CM26</t>
+          <t>2145-341-CM26</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -14935,12 +14935,12 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>61.606.409-6</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE LOS VILOS</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -14950,12 +14950,12 @@
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K238" t="inlineStr"/>
@@ -14965,7 +14965,7 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>1036.31</v>
+        <v>1200.86</v>
       </c>
     </row>
     <row r="239">
@@ -15026,13 +15026,13 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>7935.72</v>
+        <v>8025.97</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>2145-341-CM26</t>
+          <t>3714-106-CM26</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -15057,12 +15057,12 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>61.606.409-6</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE LOS VILOS</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -15072,12 +15072,12 @@
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K240" t="inlineStr"/>
@@ -15087,13 +15087,13 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>1187.35</v>
+        <v>1048.09</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>646-39-CM26</t>
+          <t>3714-105-CM26</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -15118,12 +15118,12 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>61.816.000-9</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION IV REGION</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -15133,12 +15133,12 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>MUÑOZ Y VILCHES LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>77.008.207-2</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K241" t="inlineStr"/>
@@ -15148,7 +15148,7 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>1450.45</v>
+        <v>1935.1</v>
       </c>
     </row>
     <row r="242">
@@ -15209,7 +15209,7 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>2349.45</v>
+        <v>2370.62</v>
       </c>
     </row>
     <row r="243">
@@ -15270,7 +15270,7 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>8211.799999999999</v>
+        <v>8237.639999999999</v>
       </c>
     </row>
     <row r="244">
@@ -15331,7 +15331,7 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>779.71</v>
+        <v>782.9400000000001</v>
       </c>
     </row>
     <row r="245">
@@ -15392,7 +15392,7 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>1145.65</v>
+        <v>1150.39</v>
       </c>
     </row>
     <row r="246">
@@ -15453,7 +15453,7 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>2017.68</v>
+        <v>2026.04</v>
       </c>
     </row>
     <row r="247">
@@ -15514,13 +15514,13 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>1779.82</v>
+        <v>1783.51</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>1002588-83-CM26</t>
+          <t>2125-940-CM26</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -15545,12 +15545,12 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>61.999.320-9</t>
+          <t>61.606.407-k</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE PUERTO CORDILLERA</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DR. HUMBERTO ELORZA CORTES</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -15560,32 +15560,28 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>COMERCIAL GMA SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>77.053.654-5</t>
-        </is>
-      </c>
-      <c r="K248" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr"/>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>160691.34</v>
+        <v>1806.48</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>3511-128-CM26</t>
+          <t>2145-380-CM26</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -15605,17 +15601,17 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>61.606.409-6</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE LOS VILOS</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -15625,12 +15621,12 @@
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K249" t="inlineStr"/>
@@ -15640,13 +15636,13 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>1170.73</v>
+        <v>5177.07</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>2145-380-CM26</t>
+          <t>3754-85-CM26</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -15666,17 +15662,17 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>61.606.409-6</t>
+          <t>69.041.300-0</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE LOS VILOS</t>
+          <t>I MUNICIPALIDAD DE CANELA</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -15701,13 +15697,13 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>5199.4</v>
+        <v>1772.08</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>3754-85-CM26</t>
+          <t>1002588-83-CM26</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -15727,17 +15723,17 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>69.041.300-0</t>
+          <t>61.999.320-9</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CANELA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE PUERTO CORDILLERA</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -15747,28 +15743,32 @@
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>COMERCIAL GMA SPA</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
-        </is>
-      </c>
-      <c r="K251" t="inlineStr"/>
+          <t>77.053.654-5</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L251" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>1779.73</v>
+        <v>160001.04</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>2125-940-CM26</t>
+          <t>3511-128-CM26</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -15788,17 +15788,17 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>61.606.407-k</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DR. HUMBERTO ELORZA CORTES</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -15823,7 +15823,7 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>1814.28</v>
+        <v>1165.7</v>
       </c>
     </row>
     <row r="253">
@@ -15884,7 +15884,7 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>862.4400000000001</v>
+        <v>857.27</v>
       </c>
     </row>
     <row r="254">
@@ -15945,7 +15945,7 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>22556.69</v>
+        <v>22421.5</v>
       </c>
     </row>
     <row r="255">
@@ -16006,7 +16006,7 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>1680.4</v>
+        <v>1657.56</v>
       </c>
     </row>
     <row r="256">
@@ -16067,13 +16067,13 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>1322.73</v>
+        <v>1304.75</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>1574-54-CM26</t>
+          <t>1057438-87-CM26</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -16093,17 +16093,17 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.606.401-0</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL VICUNA</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -16113,12 +16113,12 @@
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K257" t="inlineStr"/>
@@ -16128,7 +16128,7 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>12912.32</v>
+        <v>3897.63</v>
       </c>
     </row>
     <row r="258">
@@ -16189,13 +16189,13 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>48502.03</v>
+        <v>48088.34</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>1057438-87-CM26</t>
+          <t>1574-54-CM26</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -16215,17 +16215,17 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>61.606.401-0</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL VICUNA</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -16235,12 +16235,12 @@
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K259" t="inlineStr"/>
@@ -16250,7 +16250,7 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>3931.16</v>
+        <v>12802.19</v>
       </c>
     </row>
     <row r="260">
@@ -16311,13 +16311,13 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>52983.43</v>
+        <v>53268.75</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>1057439-3145-CM26</t>
+          <t>2711-115-CM26</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -16337,17 +16337,17 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>61.606.402-9</t>
+          <t>69.040.700-0</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
+          <t>MUNICIPALIDAD DE OVALLE</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -16357,12 +16357,12 @@
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>GRUPO NUVIX SPA</t>
+          <t>Comercial Agustin Limitada</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>78.209.441-6</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K261" t="inlineStr"/>
@@ -16372,13 +16372,13 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>15938.7</v>
+        <v>3007.91</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>2711-112-CM26</t>
+          <t>2711-114-CM26</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -16418,12 +16418,12 @@
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K262" t="inlineStr"/>
@@ -16433,7 +16433,7 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>1919.1</v>
+        <v>821.76</v>
       </c>
     </row>
     <row r="263">
@@ -16494,13 +16494,13 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>1830.74</v>
+        <v>1851.22</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>2711-114-CM26</t>
+          <t>2711-112-CM26</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -16540,12 +16540,12 @@
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K264" t="inlineStr"/>
@@ -16555,13 +16555,13 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>812.67</v>
+        <v>1940.56</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>2711-115-CM26</t>
+          <t>1057439-3145-CM26</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -16581,17 +16581,17 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>69.040.700-0</t>
+          <t>61.606.402-9</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE OVALLE</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -16601,12 +16601,12 @@
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>GRUPO NUVIX SPA</t>
         </is>
       </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>78.209.441-6</t>
         </is>
       </c>
       <c r="K265" t="inlineStr"/>
@@ -16616,13 +16616,13 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>2974.64</v>
+        <v>16116.95</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>1574-56-CM26</t>
+          <t>1673-118-CM26</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -16647,12 +16647,12 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.606.401-0</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL VICUNA</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -16662,12 +16662,12 @@
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K266" t="inlineStr"/>
@@ -16677,13 +16677,13 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>2210.84</v>
+        <v>859.15</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>1057438-91-CM26</t>
+          <t>1057438-90-CM26</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -16723,12 +16723,12 @@
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>DEEP FLY S.A</t>
         </is>
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>76.419.925-1</t>
         </is>
       </c>
       <c r="K267" t="inlineStr"/>
@@ -16738,13 +16738,13 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>1517.66</v>
+        <v>799.85</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>1057438-92-CM26</t>
+          <t>1057438-91-CM26</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -16784,12 +16784,12 @@
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K268" t="inlineStr"/>
@@ -16799,13 +16799,13 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>1021.78</v>
+        <v>1529.15</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>1673-118-CM26</t>
+          <t>1057438-92-CM26</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -16845,12 +16845,12 @@
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>Comercial Agustin Limitada</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K269" t="inlineStr"/>
@@ -16860,13 +16860,13 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>852.6900000000001</v>
+        <v>1029.52</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>1057438-90-CM26</t>
+          <t>1574-56-CM26</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -16891,12 +16891,12 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>61.606.401-0</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL VICUNA</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -16906,12 +16906,12 @@
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>DEEP FLY S.A</t>
+          <t>Comercial Agustin Limitada</t>
         </is>
       </c>
       <c r="J270" t="inlineStr">
         <is>
-          <t>76.419.925-1</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K270" t="inlineStr"/>
@@ -16921,7 +16921,7 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>793.84</v>
+        <v>2227.59</v>
       </c>
     </row>
     <row r="271">
@@ -16982,7 +16982,7 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>11879.84</v>
+        <v>11924.85</v>
       </c>
     </row>
     <row r="272">
@@ -17043,7 +17043,7 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>70360.74000000001</v>
+        <v>70183.10000000001</v>
       </c>
     </row>
     <row r="273">
@@ -17104,7 +17104,7 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>2715.38</v>
+        <v>2708.52</v>
       </c>
     </row>
     <row r="274">
@@ -17165,13 +17165,13 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>1346.9</v>
+        <v>1343.5</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>3712-343-CM26</t>
+          <t>5416-426-CM26</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -17196,12 +17196,12 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -17211,12 +17211,12 @@
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>GRUPO DK SERVICIOS LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J275" t="inlineStr">
         <is>
-          <t>76.556.184-1</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K275" t="inlineStr"/>
@@ -17226,13 +17226,13 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>3885.44</v>
+        <v>8449.5</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>2147-238-CM26</t>
+          <t>3712-343-CM26</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -17257,12 +17257,12 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>61.606.406-1</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL COMB</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -17272,12 +17272,12 @@
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>GRUPO DK SERVICIOS LIMITADA</t>
         </is>
       </c>
       <c r="J276" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>76.556.184-1</t>
         </is>
       </c>
       <c r="K276" t="inlineStr"/>
@@ -17287,13 +17287,13 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>3146.45</v>
+        <v>3922.35</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>5416-426-CM26</t>
+          <t>2147-238-CM26</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -17318,12 +17318,12 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>61.606.406-1</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL COMB</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -17333,12 +17333,12 @@
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>Comercial Agustin Limitada</t>
         </is>
       </c>
       <c r="J277" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K277" t="inlineStr"/>
@@ -17348,13 +17348,13 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>8369.98</v>
+        <v>3176.34</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>646-53-CM26</t>
+          <t>1430710-319-CM26</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -17379,12 +17379,12 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>61.816.000-9</t>
+          <t>61.606.403-7</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION IV REGION</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -17409,13 +17409,13 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>799.66</v>
+        <v>5332.7</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>1430710-319-CM26</t>
+          <t>646-53-CM26</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -17440,12 +17440,12 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>61.606.403-7</t>
+          <t>61.816.000-9</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION IV REGION</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -17470,13 +17470,13 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>5293.26</v>
+        <v>805.62</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>3260-54-CM26</t>
+          <t>707418-41-CM26</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -17496,17 +17496,17 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>69.041.000-1</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RIO HURTADO</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -17516,28 +17516,32 @@
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>MONARQUÍA SPA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J280" t="inlineStr">
         <is>
-          <t>78.199.695-5</t>
-        </is>
-      </c>
-      <c r="K280" t="inlineStr"/>
+          <t>77.012.870-6</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Coquimbo </t>
+        </is>
+      </c>
       <c r="L280" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>990.87</v>
+        <v>236145.99</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>3260-55-CM26</t>
+          <t>3532-72-CM26</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -17562,12 +17566,12 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>69.041.000-1</t>
+          <t>81.925.500-8</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RIO HURTADO</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -17577,12 +17581,12 @@
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K281" t="inlineStr"/>
@@ -17592,13 +17596,13 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>2263.85</v>
+        <v>1500.1</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>707418-41-CM26</t>
+          <t>3260-54-CM26</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -17618,17 +17622,17 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>69.041.000-1</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>I MUNICIPALIDAD DE RIO HURTADO</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -17638,32 +17642,28 @@
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>MONARQUÍA SPA</t>
         </is>
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
-        </is>
-      </c>
-      <c r="K282" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
-        </is>
-      </c>
+          <t>78.199.695-5</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr"/>
       <c r="L282" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>238524.74</v>
+        <v>980.99</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>3532-72-CM26</t>
+          <t>3260-55-CM26</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -17688,12 +17688,12 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>81.925.500-8</t>
+          <t>69.041.000-1</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>I MUNICIPALIDAD DE RIO HURTADO</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -17703,12 +17703,12 @@
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J283" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K283" t="inlineStr"/>
@@ -17718,7 +17718,7 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>1515.21</v>
+        <v>2241.27</v>
       </c>
     </row>
     <row r="284">
@@ -17779,7 +17779,7 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>1329.31</v>
+        <v>1323.49</v>
       </c>
     </row>
     <row r="285">
@@ -17840,13 +17840,13 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>2948.06</v>
+        <v>2935.14</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>2555-74-CM26</t>
+          <t>1346282-224-CM26</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -17871,12 +17871,12 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -17886,12 +17886,12 @@
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J286" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K286" t="inlineStr"/>
@@ -17901,13 +17901,13 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>3318.59</v>
+        <v>1619.48</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>1346282-224-CM26</t>
+          <t>2555-74-CM26</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -17932,12 +17932,12 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -17947,12 +17947,12 @@
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>Comercial Agustin Limitada</t>
         </is>
       </c>
       <c r="J287" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K287" t="inlineStr"/>
@@ -17962,7 +17962,7 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>1637.29</v>
+        <v>3282.49</v>
       </c>
     </row>
     <row r="288">
@@ -18023,7 +18023,7 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>8355.110000000001</v>
+        <v>8334.48</v>
       </c>
     </row>
     <row r="289">
@@ -18084,7 +18084,7 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>4605.49</v>
+        <v>4594.11</v>
       </c>
     </row>
     <row r="290">
@@ -18145,7 +18145,7 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>1859.54</v>
+        <v>1868.67</v>
       </c>
     </row>
     <row r="291">
@@ -18206,7 +18206,7 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>3561.6</v>
+        <v>3579.1</v>
       </c>
     </row>
     <row r="292">
@@ -18267,7 +18267,7 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>1250.52</v>
+        <v>1256.66</v>
       </c>
     </row>
     <row r="293">
@@ -18328,13 +18328,13 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>2755.24</v>
+        <v>2768.78</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>3873-8443-CM26</t>
+          <t>2710-264-CM26</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -18354,17 +18354,17 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>69.040.900-3</t>
+          <t>69.040.700-0</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUNITAQUI</t>
+          <t>MUNICIPALIDAD DE OVALLE</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -18374,12 +18374,12 @@
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K294" t="inlineStr"/>
@@ -18389,13 +18389,13 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>1786.48</v>
+        <v>1496.85</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>2710-264-CM26</t>
+          <t>3873-8443-CM26</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -18415,17 +18415,17 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>69.040.700-0</t>
+          <t>69.040.900-3</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE OVALLE</t>
+          <t>I MUNICIPALIDAD DE PUNITAQUI</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -18435,12 +18435,12 @@
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J295" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K295" t="inlineStr"/>
@@ -18450,7 +18450,7 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>1491.9</v>
+        <v>1792.4</v>
       </c>
     </row>
     <row r="296">
@@ -18511,7 +18511,7 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>6483.6</v>
+        <v>6576.37</v>
       </c>
     </row>
     <row r="297">
@@ -18572,7 +18572,7 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>2142.85</v>
+        <v>2167.99</v>
       </c>
     </row>
     <row r="298">
@@ -18633,13 +18633,13 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>4880.96</v>
+        <v>4938.22</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>1797-31-CM26</t>
+          <t>1962-309-CM26</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -18659,17 +18659,17 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>60.908.000-0</t>
+          <t>61.004.012-8</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE AUXILIO ESCOLAR Y BECA</t>
+          <t>Gendarmería de Chile - Dirección Regional de Coquimbo</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -18679,12 +18679,12 @@
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t>ROLAND VORWERK Y COMPANIA LIMITADA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J299" t="inlineStr">
         <is>
-          <t>78.178.530-k</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K299" t="inlineStr"/>
@@ -18694,13 +18694,13 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>5161.5</v>
+        <v>863.5599999999999</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>1962-309-CM26</t>
+          <t>1797-31-CM26</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -18720,17 +18720,17 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>61.004.012-8</t>
+          <t>60.908.000-0</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>Gendarmería de Chile - Dirección Regional de Coquimbo</t>
+          <t>JUNTA NACIONAL DE AUXILIO ESCOLAR Y BECA</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -18740,12 +18740,12 @@
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>ROLAND VORWERK Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J300" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>78.178.530-k</t>
         </is>
       </c>
       <c r="K300" t="inlineStr"/>
@@ -18755,7 +18755,7 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>849.1900000000001</v>
+        <v>5248.79</v>
       </c>
     </row>
     <row r="301">
@@ -18816,7 +18816,7 @@
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>1456.32</v>
+        <v>1471.13</v>
       </c>
     </row>
     <row r="302">
@@ -18877,7 +18877,7 @@
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>1384.91</v>
+        <v>1397.9</v>
       </c>
     </row>
     <row r="303">
@@ -18938,7 +18938,7 @@
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>8140.3</v>
+        <v>8216.65</v>
       </c>
     </row>
     <row r="304">
@@ -18999,13 +18999,13 @@
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>11934.05</v>
+        <v>12045.98</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>1962-322-CM26</t>
+          <t>3511-215-CM26</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -19025,17 +19025,17 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>61.004.012-8</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>Gendarmería de Chile - Dirección Regional de Coquimbo</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
@@ -19045,12 +19045,12 @@
       </c>
       <c r="I305" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>CASTILLA Y ARAGON SPA</t>
         </is>
       </c>
       <c r="J305" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>96.989.530-7</t>
         </is>
       </c>
       <c r="K305" t="inlineStr"/>
@@ -19060,13 +19060,13 @@
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>1980.82</v>
+        <v>1711.18</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>2146-284-CM26</t>
+          <t>1242121-293-CM26</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -19091,12 +19091,12 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>61.606.405-3</t>
+          <t>61.606.404-5</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE ANDACOLLO</t>
+          <t>Servicio de Salud Coquimbo Hospital de Ovalle</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
@@ -19106,12 +19106,12 @@
       </c>
       <c r="I306" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J306" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K306" t="inlineStr"/>
@@ -19121,13 +19121,13 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>1109.1</v>
+        <v>6848.65</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>3511-221-CM26</t>
+          <t>1242121-294-CM26</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -19147,17 +19147,17 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>61.606.404-5</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>Servicio de Salud Coquimbo Hospital de Ovalle</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
@@ -19182,13 +19182,13 @@
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>1242.55</v>
+        <v>3865.08</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>3511-215-CM26</t>
+          <t>3511-221-CM26</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -19228,12 +19228,12 @@
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t>CASTILLA Y ARAGON SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J308" t="inlineStr">
         <is>
-          <t>96.989.530-7</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K308" t="inlineStr"/>
@@ -19243,13 +19243,13 @@
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>1724.26</v>
+        <v>1233.12</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>1242121-293-CM26</t>
+          <t>2146-284-CM26</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -19274,12 +19274,12 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>61.606.404-5</t>
+          <t>61.606.405-3</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Servicio de Salud Coquimbo Hospital de Ovalle</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE ANDACOLLO</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
@@ -19289,12 +19289,12 @@
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J309" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K309" t="inlineStr"/>
@@ -19304,13 +19304,13 @@
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>6901</v>
+        <v>1100.69</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>1242121-294-CM26</t>
+          <t>1962-322-CM26</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -19335,12 +19335,12 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>61.606.404-5</t>
+          <t>61.004.012-8</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>Servicio de Salud Coquimbo Hospital de Ovalle</t>
+          <t>Gendarmería de Chile - Dirección Regional de Coquimbo</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
@@ -19350,12 +19350,12 @@
       </c>
       <c r="I310" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>Comercial Agustin Limitada</t>
         </is>
       </c>
       <c r="J310" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K310" t="inlineStr"/>
@@ -19365,13 +19365,13 @@
         </is>
       </c>
       <c r="M310" s="2" t="n">
-        <v>3894.62</v>
+        <v>1965.8</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>1346282-261-CM26</t>
+          <t>1962-326-CM26</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -19396,12 +19396,12 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.004.012-8</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>Gendarmería de Chile - Dirección Regional de Coquimbo</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
@@ -19411,12 +19411,12 @@
       </c>
       <c r="I311" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>Comercial Agustin Limitada</t>
         </is>
       </c>
       <c r="J311" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K311" t="inlineStr"/>
@@ -19426,13 +19426,13 @@
         </is>
       </c>
       <c r="M311" s="2" t="n">
-        <v>1340.79</v>
+        <v>1775.72</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>1962-326-CM26</t>
+          <t>1346282-261-CM26</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -19457,12 +19457,12 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>61.004.012-8</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>Gendarmería de Chile - Dirección Regional de Coquimbo</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
@@ -19472,12 +19472,12 @@
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J312" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K312" t="inlineStr"/>
@@ -19487,7 +19487,7 @@
         </is>
       </c>
       <c r="M312" s="2" t="n">
-        <v>1806.24</v>
+        <v>1318.13</v>
       </c>
     </row>
     <row r="313">
@@ -19548,7 +19548,7 @@
         </is>
       </c>
       <c r="M313" s="2" t="n">
-        <v>6213.18</v>
+        <v>6125</v>
       </c>
     </row>
     <row r="314">
@@ -19609,7 +19609,7 @@
         </is>
       </c>
       <c r="M314" s="2" t="n">
-        <v>1230.45</v>
+        <v>1212.99</v>
       </c>
     </row>
     <row r="315">
@@ -19670,7 +19670,7 @@
         </is>
       </c>
       <c r="M315" s="2" t="n">
-        <v>5503.75</v>
+        <v>5425.64</v>
       </c>
     </row>
     <row r="316">
@@ -19731,7 +19731,7 @@
         </is>
       </c>
       <c r="M316" s="2" t="n">
-        <v>3206.29</v>
+        <v>3162.23</v>
       </c>
     </row>
     <row r="317">
@@ -19792,13 +19792,13 @@
         </is>
       </c>
       <c r="M317" s="2" t="n">
-        <v>1186.36</v>
+        <v>1170.06</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>1159-146-CM26</t>
+          <t>548238-83-CM26</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -19823,12 +19823,12 @@
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
@@ -19838,12 +19838,12 @@
       </c>
       <c r="I318" t="inlineStr">
         <is>
-          <t>CHICAUMA CHILE SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J318" t="inlineStr">
         <is>
-          <t>77.935.401-6</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K318" t="inlineStr"/>
@@ -19853,13 +19853,13 @@
         </is>
       </c>
       <c r="M318" s="2" t="n">
-        <v>9168.190000000001</v>
+        <v>2132.74</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>548238-83-CM26</t>
+          <t>1159-146-CM26</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -19884,12 +19884,12 @@
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
@@ -19899,12 +19899,12 @@
       </c>
       <c r="I319" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>CHICAUMA CHILE SPA</t>
         </is>
       </c>
       <c r="J319" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>77.935.401-6</t>
         </is>
       </c>
       <c r="K319" t="inlineStr"/>
@@ -19914,7 +19914,7 @@
         </is>
       </c>
       <c r="M319" s="2" t="n">
-        <v>2146.04</v>
+        <v>9111.35</v>
       </c>
     </row>
     <row r="320">
@@ -19975,7 +19975,7 @@
         </is>
       </c>
       <c r="M320" s="2" t="n">
-        <v>8837.780000000001</v>
+        <v>8877.92</v>
       </c>
     </row>
     <row r="321">
@@ -20036,13 +20036,13 @@
         </is>
       </c>
       <c r="M321" s="2" t="n">
-        <v>1561.01</v>
+        <v>1568.1</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>1057439-4171-CM26</t>
+          <t>5416-591-CM26</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -20067,12 +20067,12 @@
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>61.606.402-9</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
@@ -20082,12 +20082,12 @@
       </c>
       <c r="I322" t="inlineStr">
         <is>
-          <t>GRUPO NUVIX SPA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J322" t="inlineStr">
         <is>
-          <t>78.209.441-6</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K322" t="inlineStr"/>
@@ -20097,7 +20097,7 @@
         </is>
       </c>
       <c r="M322" s="2" t="n">
-        <v>14261.17</v>
+        <v>2780.47</v>
       </c>
     </row>
     <row r="323">
@@ -20158,13 +20158,13 @@
         </is>
       </c>
       <c r="M323" s="2" t="n">
-        <v>5008.61</v>
+        <v>5103.83</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>5416-591-CM26</t>
+          <t>1057439-4171-CM26</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -20189,12 +20189,12 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>61.606.402-9</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
@@ -20204,12 +20204,12 @@
       </c>
       <c r="I324" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>GRUPO NUVIX SPA</t>
         </is>
       </c>
       <c r="J324" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>78.209.441-6</t>
         </is>
       </c>
       <c r="K324" t="inlineStr"/>
@@ -20219,7 +20219,7 @@
         </is>
       </c>
       <c r="M324" s="2" t="n">
-        <v>2728.59</v>
+        <v>14532.3</v>
       </c>
     </row>
     <row r="325">
@@ -20280,7 +20280,7 @@
         </is>
       </c>
       <c r="M325" s="2" t="n">
-        <v>6159.55</v>
+        <v>6298.46</v>
       </c>
     </row>
     <row r="326">
@@ -20341,7 +20341,7 @@
         </is>
       </c>
       <c r="M326" s="2" t="n">
-        <v>908.09</v>
+        <v>928.5700000000001</v>
       </c>
     </row>
     <row r="327">
@@ -20402,7 +20402,7 @@
         </is>
       </c>
       <c r="M327" s="2" t="n">
-        <v>837.65</v>
+        <v>856.54</v>
       </c>
     </row>
     <row r="328">
@@ -20463,7 +20463,7 @@
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>1890.42</v>
+        <v>1903.47</v>
       </c>
     </row>
     <row r="329">
@@ -20524,7 +20524,7 @@
         </is>
       </c>
       <c r="M329" s="2" t="n">
-        <v>2459.76</v>
+        <v>2476.74</v>
       </c>
     </row>
     <row r="330">
@@ -20585,7 +20585,7 @@
         </is>
       </c>
       <c r="M330" s="2" t="n">
-        <v>3721.84</v>
+        <v>3733.34</v>
       </c>
     </row>
     <row r="331">
@@ -20646,7 +20646,7 @@
         </is>
       </c>
       <c r="M331" s="2" t="n">
-        <v>4446.64</v>
+        <v>4460.39</v>
       </c>
     </row>
     <row r="332">
@@ -20707,13 +20707,13 @@
         </is>
       </c>
       <c r="M332" s="2" t="n">
-        <v>5903.03</v>
+        <v>5887.42</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>2288-569-CM26</t>
+          <t>5416-631-CM26</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -20738,12 +20738,12 @@
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>69.041.300-0</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CANELA</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
@@ -20768,13 +20768,13 @@
         </is>
       </c>
       <c r="M333" s="2" t="n">
-        <v>1582.55</v>
+        <v>4849.19</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>2450-690-CM26</t>
+          <t>2446-719-CM26</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -20794,17 +20794,17 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>69.040.100-2</t>
+          <t>69.040.300-5</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA SERENA</t>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
@@ -20814,12 +20814,12 @@
       </c>
       <c r="I334" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J334" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K334" t="inlineStr"/>
@@ -20829,13 +20829,13 @@
         </is>
       </c>
       <c r="M334" s="2" t="n">
-        <v>29581.09</v>
+        <v>4070.34</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>5416-630-CM26</t>
+          <t>2288-569-CM26</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -20860,12 +20860,12 @@
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>69.041.300-0</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>I MUNICIPALIDAD DE CANELA</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
@@ -20875,12 +20875,12 @@
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J335" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K335" t="inlineStr"/>
@@ -20890,13 +20890,13 @@
         </is>
       </c>
       <c r="M335" s="2" t="n">
-        <v>990.85</v>
+        <v>1561.47</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>2446-719-CM26</t>
+          <t>2450-690-CM26</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -20916,17 +20916,17 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>69.040.300-5</t>
+          <t>69.040.100-2</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+          <t>I MUNICIPALIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
@@ -20936,12 +20936,12 @@
       </c>
       <c r="I336" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J336" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K336" t="inlineStr"/>
@@ -20951,13 +20951,13 @@
         </is>
       </c>
       <c r="M336" s="2" t="n">
-        <v>4125.29</v>
+        <v>29187.07</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>5416-631-CM26</t>
+          <t>5416-630-CM26</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -20997,12 +20997,12 @@
       </c>
       <c r="I337" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J337" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K337" t="inlineStr"/>
@@ -21012,7 +21012,7 @@
         </is>
       </c>
       <c r="M337" s="2" t="n">
-        <v>4914.65</v>
+        <v>977.65</v>
       </c>
     </row>
     <row r="338">
@@ -21073,7 +21073,7 @@
         </is>
       </c>
       <c r="M338" s="2" t="n">
-        <v>8807.26</v>
+        <v>8634.870000000001</v>
       </c>
     </row>
     <row r="339">
@@ -21134,13 +21134,13 @@
         </is>
       </c>
       <c r="M339" s="2" t="n">
-        <v>899.24</v>
+        <v>907.78</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>646-70-CM26</t>
+          <t>3712-437-CM26</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -21165,12 +21165,12 @@
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>61.816.000-9</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION IV REGION</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
@@ -21180,12 +21180,12 @@
       </c>
       <c r="I340" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J340" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K340" t="inlineStr"/>
@@ -21195,7 +21195,7 @@
         </is>
       </c>
       <c r="M340" s="2" t="n">
-        <v>1374.94</v>
+        <v>8285.84</v>
       </c>
     </row>
     <row r="341">
@@ -21256,13 +21256,13 @@
         </is>
       </c>
       <c r="M341" s="2" t="n">
-        <v>2787.83</v>
+        <v>2815.87</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>3712-437-CM26</t>
+          <t>646-70-CM26</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -21287,12 +21287,12 @@
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>61.816.000-9</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION IV REGION</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
@@ -21302,12 +21302,12 @@
       </c>
       <c r="I342" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>Comercial Agustin Limitada</t>
         </is>
       </c>
       <c r="J342" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K342" t="inlineStr"/>
@@ -21317,13 +21317,13 @@
         </is>
       </c>
       <c r="M342" s="2" t="n">
-        <v>8203.34</v>
+        <v>1388.76</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>2448-547-CM26</t>
+          <t>5416-677-CM26</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -21343,17 +21343,17 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>69.040.300-5</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
@@ -21363,12 +21363,12 @@
       </c>
       <c r="I343" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J343" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K343" t="inlineStr"/>
@@ -21378,13 +21378,13 @@
         </is>
       </c>
       <c r="M343" s="2" t="n">
-        <v>14549.71</v>
+        <v>2067.21</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>3712-452-CM26</t>
+          <t>5416-676-CM26</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -21409,12 +21409,12 @@
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
@@ -21424,12 +21424,12 @@
       </c>
       <c r="I344" t="inlineStr">
         <is>
-          <t>GRUPO DK SERVICIOS LIMITADA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J344" t="inlineStr">
         <is>
-          <t>76.556.184-1</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K344" t="inlineStr"/>
@@ -21439,13 +21439,13 @@
         </is>
       </c>
       <c r="M344" s="2" t="n">
-        <v>5383.46</v>
+        <v>1764.33</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>3712-458-CM26</t>
+          <t>2552-13-CM26</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -21470,12 +21470,12 @@
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
@@ -21500,13 +21500,13 @@
         </is>
       </c>
       <c r="M345" s="2" t="n">
-        <v>7891.07</v>
+        <v>777.5</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>2552-13-CM26</t>
+          <t>2125-1377-CM26</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -21531,12 +21531,12 @@
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.606.407-k</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DR. HUMBERTO ELORZA CORTES</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
@@ -21561,13 +21561,13 @@
         </is>
       </c>
       <c r="M346" s="2" t="n">
-        <v>769.8</v>
+        <v>1943.13</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>2125-1377-CM26</t>
+          <t>3712-452-CM26</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -21592,12 +21592,12 @@
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>61.606.407-k</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DR. HUMBERTO ELORZA CORTES</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
@@ -21607,12 +21607,12 @@
       </c>
       <c r="I347" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>GRUPO DK SERVICIOS LIMITADA</t>
         </is>
       </c>
       <c r="J347" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.556.184-1</t>
         </is>
       </c>
       <c r="K347" t="inlineStr"/>
@@ -21622,13 +21622,13 @@
         </is>
       </c>
       <c r="M347" s="2" t="n">
-        <v>1923.86</v>
+        <v>5437.37</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>5416-676-CM26</t>
+          <t>2448-547-CM26</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -21648,17 +21648,17 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>69.040.300-5</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
@@ -21668,12 +21668,12 @@
       </c>
       <c r="I348" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>Comercial Agustin Limitada</t>
         </is>
       </c>
       <c r="J348" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K348" t="inlineStr"/>
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="M348" s="2" t="n">
-        <v>1746.84</v>
+        <v>14695.4</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>5416-677-CM26</t>
+          <t>3712-458-CM26</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -21714,12 +21714,12 @@
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
@@ -21729,12 +21729,12 @@
       </c>
       <c r="I349" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J349" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K349" t="inlineStr"/>
@@ -21744,7 +21744,7 @@
         </is>
       </c>
       <c r="M349" s="2" t="n">
-        <v>2046.71</v>
+        <v>7970.09</v>
       </c>
     </row>
     <row r="350">
@@ -21805,7 +21805,7 @@
         </is>
       </c>
       <c r="M350" s="2" t="n">
-        <v>4624.61</v>
+        <v>4648.17</v>
       </c>
     </row>
     <row r="351">
@@ -21866,13 +21866,13 @@
         </is>
       </c>
       <c r="M351" s="2" t="n">
-        <v>9548.24</v>
+        <v>9596.889999999999</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>1242121-351-CM26</t>
+          <t>3714-176-CM26</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -21897,12 +21897,12 @@
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>61.606.404-5</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>Servicio de Salud Coquimbo Hospital de Ovalle</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
@@ -21912,12 +21912,12 @@
       </c>
       <c r="I352" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J352" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K352" t="inlineStr"/>
@@ -21927,7 +21927,7 @@
         </is>
       </c>
       <c r="M352" s="2" t="n">
-        <v>6596.31</v>
+        <v>5410.65</v>
       </c>
     </row>
     <row r="353">
@@ -21988,13 +21988,13 @@
         </is>
       </c>
       <c r="M353" s="2" t="n">
-        <v>2424.43</v>
+        <v>2433.87</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>3714-176-CM26</t>
+          <t>1242121-351-CM26</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -22019,12 +22019,12 @@
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>61.606.404-5</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>Servicio de Salud Coquimbo Hospital de Ovalle</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
@@ -22034,12 +22034,12 @@
       </c>
       <c r="I354" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J354" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K354" t="inlineStr"/>
@@ -22049,7 +22049,7 @@
         </is>
       </c>
       <c r="M354" s="2" t="n">
-        <v>5389.67</v>
+        <v>6621.99</v>
       </c>
     </row>
     <row r="355">
@@ -22110,7 +22110,7 @@
         </is>
       </c>
       <c r="M355" s="2" t="n">
-        <v>2521.13</v>
+        <v>2508.36</v>
       </c>
     </row>
     <row r="356">
@@ -22171,13 +22171,13 @@
         </is>
       </c>
       <c r="M356" s="2" t="n">
-        <v>2752.48</v>
+        <v>2738.54</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>3712-484-CM26</t>
+          <t>3707-364-CM26</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -22197,17 +22197,17 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.040.200-9</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>I MUNICIPALIDAD DE LA HIGUERA</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
@@ -22217,12 +22217,12 @@
       </c>
       <c r="I357" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J357" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K357" t="inlineStr"/>
@@ -22232,13 +22232,13 @@
         </is>
       </c>
       <c r="M357" s="2" t="n">
-        <v>6012.83</v>
+        <v>2309.96</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>3509-285-CM26</t>
+          <t>1057439-4602-CM26</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -22263,12 +22263,12 @@
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>61.606.402-9</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
         </is>
       </c>
       <c r="H358" t="inlineStr">
@@ -22278,12 +22278,12 @@
       </c>
       <c r="I358" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>GRUPO NUVIX SPA</t>
         </is>
       </c>
       <c r="J358" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>78.209.441-6</t>
         </is>
       </c>
       <c r="K358" t="inlineStr"/>
@@ -22293,13 +22293,13 @@
         </is>
       </c>
       <c r="M358" s="2" t="n">
-        <v>929.98</v>
+        <v>17228.72</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>1057439-4602-CM26</t>
+          <t>3712-484-CM26</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -22319,17 +22319,17 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>61.606.402-9</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
@@ -22339,12 +22339,12 @@
       </c>
       <c r="I359" t="inlineStr">
         <is>
-          <t>GRUPO NUVIX SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J359" t="inlineStr">
         <is>
-          <t>78.209.441-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K359" t="inlineStr"/>
@@ -22354,13 +22354,13 @@
         </is>
       </c>
       <c r="M359" s="2" t="n">
-        <v>17192.07</v>
+        <v>6025.64</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>3707-364-CM26</t>
+          <t>3509-285-CM26</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -22385,12 +22385,12 @@
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>69.040.200-9</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA HIGUERA</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H360" t="inlineStr">
@@ -22400,12 +22400,12 @@
       </c>
       <c r="I360" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>Comercial Agustin Limitada</t>
         </is>
       </c>
       <c r="J360" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K360" t="inlineStr"/>
@@ -22415,7 +22415,7 @@
         </is>
       </c>
       <c r="M360" s="2" t="n">
-        <v>2305.04</v>
+        <v>931.97</v>
       </c>
     </row>
     <row r="361">
@@ -22476,7 +22476,7 @@
         </is>
       </c>
       <c r="M361" s="2" t="n">
-        <v>6031.58</v>
+        <v>6044.44</v>
       </c>
     </row>
     <row r="362">
@@ -22537,13 +22537,13 @@
         </is>
       </c>
       <c r="M362" s="2" t="n">
-        <v>1261.01</v>
+        <v>1269.23</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>3713-87-CM26</t>
+          <t>3712-476-CM26</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -22583,12 +22583,12 @@
       </c>
       <c r="I363" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>Comercial Agustin Limitada</t>
         </is>
       </c>
       <c r="J363" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K363" t="inlineStr"/>
@@ -22598,13 +22598,13 @@
         </is>
       </c>
       <c r="M363" s="2" t="n">
-        <v>2849.32</v>
+        <v>2041.86</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>3614-195-CM26</t>
+          <t>3713-87-CM26</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -22624,17 +22624,17 @@
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>69.040.500-8</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VICUNA</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
@@ -22659,13 +22659,13 @@
         </is>
       </c>
       <c r="M364" s="2" t="n">
-        <v>1311.92</v>
+        <v>2855.86</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>3712-476-CM26</t>
+          <t>3614-195-CM26</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -22685,17 +22685,17 @@
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.040.500-8</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>I MUNICIPALIDAD DE VICUNA</t>
         </is>
       </c>
       <c r="H365" t="inlineStr">
@@ -22705,12 +22705,12 @@
       </c>
       <c r="I365" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J365" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K365" t="inlineStr"/>
@@ -22720,7 +22720,7 @@
         </is>
       </c>
       <c r="M365" s="2" t="n">
-        <v>2037.19</v>
+        <v>1314.93</v>
       </c>
     </row>
     <row r="366">
@@ -22781,7 +22781,7 @@
         </is>
       </c>
       <c r="M366" s="2" t="n">
-        <v>3269.08</v>
+        <v>3290.96</v>
       </c>
     </row>
     <row r="367">
@@ -22842,7 +22842,7 @@
         </is>
       </c>
       <c r="M367" s="2" t="n">
-        <v>859.45</v>
+        <v>856.73</v>
       </c>
     </row>
     <row r="368">
@@ -22903,13 +22903,13 @@
         </is>
       </c>
       <c r="M368" s="2" t="n">
-        <v>68818</v>
+        <v>68419.67</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>2125-1444-CM26</t>
+          <t>2708-402-CM26</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -22929,17 +22929,17 @@
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>61.606.407-k</t>
+          <t>69.040.700-0</t>
         </is>
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DR. HUMBERTO ELORZA CORTES</t>
+          <t>MUNICIPALIDAD DE OVALLE</t>
         </is>
       </c>
       <c r="H369" t="inlineStr">
@@ -22949,12 +22949,12 @@
       </c>
       <c r="I369" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J369" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K369" t="inlineStr"/>
@@ -22964,13 +22964,13 @@
         </is>
       </c>
       <c r="M369" s="2" t="n">
-        <v>910.08</v>
+        <v>1790.91</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>2708-402-CM26</t>
+          <t>2125-1444-CM26</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -22990,17 +22990,17 @@
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>69.040.700-0</t>
+          <t>61.606.407-k</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE OVALLE</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DR. HUMBERTO ELORZA CORTES</t>
         </is>
       </c>
       <c r="H370" t="inlineStr">
@@ -23010,12 +23010,12 @@
       </c>
       <c r="I370" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J370" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K370" t="inlineStr"/>
@@ -23025,7 +23025,7 @@
         </is>
       </c>
       <c r="M370" s="2" t="n">
-        <v>1820.28</v>
+        <v>895.39</v>
       </c>
     </row>
     <row r="371">
@@ -23086,7 +23086,7 @@
         </is>
       </c>
       <c r="M371" s="2" t="n">
-        <v>13663.58</v>
+        <v>13444.5</v>
       </c>
     </row>
     <row r="372">
@@ -23147,7 +23147,7 @@
         </is>
       </c>
       <c r="M372" s="2" t="n">
-        <v>908.23</v>
+        <v>897.66</v>
       </c>
     </row>
     <row r="373">
@@ -23208,13 +23208,13 @@
         </is>
       </c>
       <c r="M373" s="2" t="n">
-        <v>2334.25</v>
+        <v>2307.09</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>2147-375-CM26</t>
+          <t>4433-50-CM26</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -23239,12 +23239,12 @@
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>61.606.406-1</t>
+          <t>69.040.600-4</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL COMB</t>
+          <t>I MUNICIPALIDAD PAIHUANO</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
@@ -23254,12 +23254,12 @@
       </c>
       <c r="I374" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J374" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K374" t="inlineStr"/>
@@ -23269,13 +23269,13 @@
         </is>
       </c>
       <c r="M374" s="2" t="n">
-        <v>3919.6</v>
+        <v>2568.34</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>4433-50-CM26</t>
+          <t>2448-780-CM26</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -23300,12 +23300,12 @@
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>69.040.600-4</t>
+          <t>69.040.300-5</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD PAIHUANO</t>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
         </is>
       </c>
       <c r="H375" t="inlineStr">
@@ -23315,12 +23315,12 @@
       </c>
       <c r="I375" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>MONARQUÍA SPA</t>
         </is>
       </c>
       <c r="J375" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>78.199.695-5</t>
         </is>
       </c>
       <c r="K375" t="inlineStr"/>
@@ -23330,13 +23330,13 @@
         </is>
       </c>
       <c r="M375" s="2" t="n">
-        <v>2581.03</v>
+        <v>2288.58</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>2448-780-CM26</t>
+          <t>2147-375-CM26</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -23361,12 +23361,12 @@
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>69.040.300-5</t>
+          <t>61.606.406-1</t>
         </is>
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL COMB</t>
         </is>
       </c>
       <c r="H376" t="inlineStr">
@@ -23376,12 +23376,12 @@
       </c>
       <c r="I376" t="inlineStr">
         <is>
-          <t>MONARQUÍA SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J376" t="inlineStr">
         <is>
-          <t>78.199.695-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K376" t="inlineStr"/>
@@ -23391,7 +23391,7 @@
         </is>
       </c>
       <c r="M376" s="2" t="n">
-        <v>2299.89</v>
+        <v>3900.33</v>
       </c>
     </row>
     <row r="377">
@@ -23452,7 +23452,190 @@
         </is>
       </c>
       <c r="M377" s="2" t="n">
-        <v>1722.46</v>
+        <v>1733.99</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>3509-314-CM26</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>69.041.200-4</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+        </is>
+      </c>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I378" t="inlineStr">
+        <is>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
+        </is>
+      </c>
+      <c r="J378" t="inlineStr">
+        <is>
+          <t>76.287.853-4</t>
+        </is>
+      </c>
+      <c r="K378" t="inlineStr"/>
+      <c r="L378" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M378" s="2" t="n">
+        <v>1511.16</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>1057438-203-CM26</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>61.606.401-0</t>
+        </is>
+      </c>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL VICUNA</t>
+        </is>
+      </c>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I379" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J379" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K379" t="inlineStr"/>
+      <c r="L379" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M379" s="2" t="n">
+        <v>8382.32</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>2125-1591-CM26</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>61.606.407-k</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DR. HUMBERTO ELORZA CORTES</t>
+        </is>
+      </c>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I380" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J380" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K380" t="inlineStr"/>
+      <c r="L380" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M380" s="2" t="n">
+        <v>4141.36</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/articulos-de-aseo-e-higiene/coquimbo.xlsx
+++ b/docs/oc-regiones/articulos-de-aseo-e-higiene/coquimbo.xlsx
@@ -562,7 +562,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +948,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1135,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1322,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1387,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1452,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1639,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1704,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1769,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1834,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1960,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2086,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2212,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2277,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2342,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2407,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2472,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2537,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2602,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2728,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2854,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +2980,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3045,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3171,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3236,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3301,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3366,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3492,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3557,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3551,7 +3683,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3612,7 +3748,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3813,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3878,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3795,7 +3943,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3856,7 +4008,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3917,7 +4073,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4199,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4325,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4283,7 +4451,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4344,7 +4516,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4581,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4466,7 +4646,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4527,7 +4711,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4588,7 +4776,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4649,7 +4841,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4710,7 +4906,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4832,7 +5032,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4893,7 +5097,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4954,7 +5162,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5015,7 +5227,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5076,7 +5292,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5137,7 +5357,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5320,7 +5544,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5381,7 +5609,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5442,7 +5674,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5503,7 +5739,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5564,7 +5804,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5625,7 +5869,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5686,7 +5934,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5747,7 +5999,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5808,7 +6064,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5869,7 +6129,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5991,7 +6255,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6052,7 +6320,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6113,7 +6385,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6174,7 +6450,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6235,7 +6515,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6296,7 +6580,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6357,7 +6645,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6418,7 +6710,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6479,7 +6775,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6540,7 +6840,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6784,7 +7088,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6845,7 +7153,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6906,7 +7218,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7028,7 +7344,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7089,7 +7409,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7150,7 +7474,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7211,7 +7539,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7272,7 +7604,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7333,7 +7669,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7394,7 +7734,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7455,7 +7799,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7516,7 +7864,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7638,7 +7990,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7699,7 +8055,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7760,7 +8120,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7821,7 +8185,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7882,7 +8250,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7943,7 +8315,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8126,7 +8502,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8187,7 +8567,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8309,7 +8693,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8370,7 +8758,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8492,7 +8884,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8553,7 +8949,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8736,7 +9136,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8797,7 +9201,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8858,7 +9266,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8919,7 +9331,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9041,7 +9457,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9102,7 +9522,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9285,7 +9709,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9407,7 +9835,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9468,7 +9900,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9529,7 +9965,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9590,7 +10030,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9712,7 +10156,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9773,7 +10221,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9834,7 +10286,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9956,7 +10412,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10017,7 +10477,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10078,7 +10542,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10139,7 +10607,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10200,7 +10672,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10261,7 +10737,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10322,7 +10802,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10444,7 +10928,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10505,7 +10993,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10566,7 +11058,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10688,7 +11184,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10749,7 +11249,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10810,7 +11314,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10871,7 +11379,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11054,7 +11566,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11237,7 +11753,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11359,7 +11879,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11420,7 +11944,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11542,7 +12070,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11664,7 +12196,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11725,7 +12261,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11847,7 +12387,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11908,7 +12452,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12213,7 +12761,11 @@
           <t>76.556.184-1</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L193" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12335,7 +12887,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12396,7 +12952,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12701,7 +13261,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12823,7 +13387,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12884,7 +13452,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12945,7 +13517,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13006,7 +13582,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13067,7 +13647,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13250,7 +13834,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13311,7 +13899,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13372,7 +13964,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L212" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13433,7 +14029,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13494,7 +14094,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13555,7 +14159,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13616,7 +14224,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L216" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13677,7 +14289,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13799,7 +14415,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13860,7 +14480,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L220" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13982,7 +14606,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr"/>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L222" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14043,7 +14671,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L223" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14104,7 +14736,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L224" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14165,7 +14801,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14287,7 +14927,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14348,7 +14992,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14409,7 +15057,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L229" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14470,7 +15122,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L230" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14531,7 +15187,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L231" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14592,7 +15252,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14653,7 +15317,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L233" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14714,7 +15382,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L234" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14775,7 +15447,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr"/>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L235" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14836,7 +15512,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L236" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14897,7 +15577,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr"/>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L237" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14958,7 +15642,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr"/>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L238" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15019,7 +15707,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr"/>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L239" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15080,7 +15772,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr"/>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L240" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15263,7 +15959,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr"/>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L243" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15324,7 +16024,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr"/>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L244" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15385,7 +16089,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr"/>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L245" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15507,7 +16215,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr"/>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L247" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15568,7 +16280,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15629,7 +16345,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr"/>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L249" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15690,7 +16410,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr"/>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L250" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15751,7 +16475,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr"/>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L251" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15812,7 +16540,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr"/>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L252" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15873,7 +16605,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr"/>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L253" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15934,7 +16670,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr"/>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L254" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16117,7 +16857,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr"/>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L257" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16178,7 +16922,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr"/>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L258" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16239,7 +16987,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr"/>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L259" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16300,7 +17052,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr"/>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L260" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16361,7 +17117,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr"/>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L261" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16422,7 +17182,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr"/>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L262" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16483,7 +17247,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr"/>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L263" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16544,7 +17312,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr"/>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L264" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16605,7 +17377,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr"/>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L265" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16666,7 +17442,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K266" t="inlineStr"/>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L266" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16727,7 +17507,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr"/>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L267" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16788,7 +17572,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K268" t="inlineStr"/>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L268" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16849,7 +17637,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr"/>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L269" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16910,7 +17702,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K270" t="inlineStr"/>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L270" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16971,7 +17767,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr"/>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L271" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17032,7 +17832,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr"/>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L272" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17093,7 +17897,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr"/>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L273" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17154,7 +17962,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K274" t="inlineStr"/>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L274" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17215,7 +18027,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K275" t="inlineStr"/>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L275" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17337,7 +18153,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K277" t="inlineStr"/>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L277" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17459,7 +18279,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K279" t="inlineStr"/>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L279" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17581,7 +18405,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr"/>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L281" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17642,7 +18470,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K282" t="inlineStr"/>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L282" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17703,7 +18535,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K283" t="inlineStr"/>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L283" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17764,7 +18600,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K284" t="inlineStr"/>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L284" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17825,7 +18665,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K285" t="inlineStr"/>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L285" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17947,7 +18791,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K287" t="inlineStr"/>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L287" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18008,7 +18856,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K288" t="inlineStr"/>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L288" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18130,7 +18982,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K290" t="inlineStr"/>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L290" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18191,7 +19047,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K291" t="inlineStr"/>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L291" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18313,7 +19173,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K293" t="inlineStr"/>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L293" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18435,7 +19299,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K295" t="inlineStr"/>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L295" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18496,7 +19364,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K296" t="inlineStr"/>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L296" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18557,7 +19429,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K297" t="inlineStr"/>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L297" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18618,7 +19494,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K298" t="inlineStr"/>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L298" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18740,7 +19620,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K300" t="inlineStr"/>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L300" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18801,7 +19685,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K301" t="inlineStr"/>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L301" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18862,7 +19750,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K302" t="inlineStr"/>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L302" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18923,7 +19815,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K303" t="inlineStr"/>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L303" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18984,7 +19880,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K304" t="inlineStr"/>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L304" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19106,7 +20006,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K306" t="inlineStr"/>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L306" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19167,7 +20071,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K307" t="inlineStr"/>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L307" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19228,7 +20136,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K308" t="inlineStr"/>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L308" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19289,7 +20201,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K309" t="inlineStr"/>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L309" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19411,7 +20327,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K311" t="inlineStr"/>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L311" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19533,7 +20453,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K313" t="inlineStr"/>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L313" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19594,7 +20518,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K314" t="inlineStr"/>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L314" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19716,7 +20644,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K316" t="inlineStr"/>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L316" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19777,7 +20709,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K317" t="inlineStr"/>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L317" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19838,7 +20774,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K318" t="inlineStr"/>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L318" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19899,7 +20839,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K319" t="inlineStr"/>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L319" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19960,7 +20904,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K320" t="inlineStr"/>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L320" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20021,7 +20969,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K321" t="inlineStr"/>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L321" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20082,7 +21034,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K322" t="inlineStr"/>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L322" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20143,7 +21099,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K323" t="inlineStr"/>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L323" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20204,7 +21164,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K324" t="inlineStr"/>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L324" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20326,7 +21290,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K326" t="inlineStr"/>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L326" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20387,7 +21355,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K327" t="inlineStr"/>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L327" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20570,7 +21542,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K330" t="inlineStr"/>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L330" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20631,7 +21607,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K331" t="inlineStr"/>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L331" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20692,7 +21672,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K332" t="inlineStr"/>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L332" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20814,7 +21798,11 @@
           <t>77.577.274-3</t>
         </is>
       </c>
-      <c r="K334" t="inlineStr"/>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L334" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20875,7 +21863,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K335" t="inlineStr"/>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L335" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20936,7 +21928,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K336" t="inlineStr"/>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L336" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20997,7 +21993,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K337" t="inlineStr"/>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L337" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21058,7 +22058,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K338" t="inlineStr"/>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L338" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21119,7 +22123,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K339" t="inlineStr"/>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L339" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21180,7 +22188,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K340" t="inlineStr"/>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L340" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21241,7 +22253,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K341" t="inlineStr"/>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L341" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21302,7 +22318,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K342" t="inlineStr"/>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L342" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21363,7 +22383,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K343" t="inlineStr"/>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L343" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21424,7 +22448,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K344" t="inlineStr"/>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L344" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21485,7 +22513,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K345" t="inlineStr"/>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L345" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21546,7 +22578,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K346" t="inlineStr"/>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L346" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21607,7 +22643,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K347" t="inlineStr"/>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L347" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21668,7 +22708,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K348" t="inlineStr"/>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L348" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21729,7 +22773,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K349" t="inlineStr"/>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L349" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21790,7 +22838,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K350" t="inlineStr"/>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L350" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21851,7 +22903,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K351" t="inlineStr"/>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L351" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21912,7 +22968,11 @@
           <t>78.057.703-7</t>
         </is>
       </c>
-      <c r="K352" t="inlineStr"/>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L352" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21973,7 +23033,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K353" t="inlineStr"/>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L353" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22034,7 +23098,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K354" t="inlineStr"/>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L354" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22095,7 +23163,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K355" t="inlineStr"/>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L355" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22156,7 +23228,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K356" t="inlineStr"/>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L356" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22217,7 +23293,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K357" t="inlineStr"/>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L357" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22278,7 +23358,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K358" t="inlineStr"/>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L358" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22339,7 +23423,11 @@
           <t>78.209.441-6</t>
         </is>
       </c>
-      <c r="K359" t="inlineStr"/>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L359" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22400,7 +23488,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K360" t="inlineStr"/>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L360" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22461,7 +23553,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K361" t="inlineStr"/>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L361" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22522,7 +23618,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K362" t="inlineStr"/>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L362" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22583,7 +23683,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K363" t="inlineStr"/>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L363" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22644,7 +23748,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K364" t="inlineStr"/>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L364" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22766,7 +23874,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K366" t="inlineStr"/>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L366" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22827,7 +23939,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K367" t="inlineStr"/>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L367" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22888,7 +24004,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K368" t="inlineStr"/>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L368" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23071,7 +24191,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K371" t="inlineStr"/>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L371" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23132,7 +24256,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K372" t="inlineStr"/>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L372" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23193,7 +24321,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K373" t="inlineStr"/>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L373" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23254,7 +24386,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K374" t="inlineStr"/>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L374" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23315,7 +24451,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K375" t="inlineStr"/>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L375" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23376,7 +24516,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K376" t="inlineStr"/>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L376" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23437,7 +24581,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K377" t="inlineStr"/>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L377" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23498,7 +24646,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K378" t="inlineStr"/>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L378" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23559,7 +24711,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K379" t="inlineStr"/>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L379" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23620,7 +24776,11 @@
           <t>78.076.237-3</t>
         </is>
       </c>
-      <c r="K380" t="inlineStr"/>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L380" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23681,7 +24841,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K381" t="inlineStr"/>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L381" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23742,7 +24906,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K382" t="inlineStr"/>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L382" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23803,7 +24971,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K383" t="inlineStr"/>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L383" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23925,7 +25097,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K385" t="inlineStr"/>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L385" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23986,7 +25162,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K386" t="inlineStr"/>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L386" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24047,7 +25227,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K387" t="inlineStr"/>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L387" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24108,7 +25292,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K388" t="inlineStr"/>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L388" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24169,7 +25357,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K389" t="inlineStr"/>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L389" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24230,7 +25422,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K390" t="inlineStr"/>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L390" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24291,7 +25487,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K391" t="inlineStr"/>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L391" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24474,7 +25674,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K394" t="inlineStr"/>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L394" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24535,7 +25739,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K395" t="inlineStr"/>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L395" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24596,7 +25804,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K396" t="inlineStr"/>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L396" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24657,7 +25869,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K397" t="inlineStr"/>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L397" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24718,7 +25934,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K398" t="inlineStr"/>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L398" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24779,7 +25999,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K399" t="inlineStr"/>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L399" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24840,7 +26064,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K400" t="inlineStr"/>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L400" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24901,7 +26129,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K401" t="inlineStr"/>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L401" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24962,7 +26194,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K402" t="inlineStr"/>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L402" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25023,7 +26259,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K403" t="inlineStr"/>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L403" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25084,7 +26324,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K404" t="inlineStr"/>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L404" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25145,7 +26389,11 @@
           <t>78.209.441-6</t>
         </is>
       </c>
-      <c r="K405" t="inlineStr"/>
+      <c r="K405" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L405" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25267,7 +26515,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K407" t="inlineStr"/>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L407" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25328,7 +26580,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K408" t="inlineStr"/>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L408" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25450,7 +26706,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K410" t="inlineStr"/>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L410" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25511,7 +26771,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K411" t="inlineStr"/>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L411" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25572,7 +26836,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K412" t="inlineStr"/>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L412" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25633,7 +26901,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K413" t="inlineStr"/>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L413" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25694,7 +26966,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K414" t="inlineStr"/>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L414" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25755,7 +27031,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K415" t="inlineStr"/>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L415" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25816,7 +27096,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K416" t="inlineStr"/>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L416" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25877,7 +27161,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K417" t="inlineStr"/>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L417" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25938,7 +27226,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K418" t="inlineStr"/>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L418" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25999,7 +27291,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K419" t="inlineStr"/>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L419" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26060,7 +27356,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K420" t="inlineStr"/>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L420" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26121,7 +27421,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K421" t="inlineStr"/>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L421" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26182,7 +27486,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K422" t="inlineStr"/>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L422" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26243,7 +27551,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K423" t="inlineStr"/>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L423" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26304,7 +27616,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K424" t="inlineStr"/>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L424" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26365,7 +27681,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K425" t="inlineStr"/>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L425" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26426,7 +27746,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K426" t="inlineStr"/>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L426" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26548,7 +27872,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K428" t="inlineStr"/>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L428" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26609,7 +27937,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K429" t="inlineStr"/>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L429" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26670,7 +28002,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K430" t="inlineStr"/>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L430" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26731,7 +28067,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K431" t="inlineStr"/>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L431" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26853,7 +28193,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K433" t="inlineStr"/>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L433" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26975,7 +28319,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K435" t="inlineStr"/>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L435" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27036,7 +28384,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K436" t="inlineStr"/>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L436" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27097,7 +28449,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K437" t="inlineStr"/>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L437" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27158,7 +28514,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K438" t="inlineStr"/>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L438" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27219,7 +28579,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K439" t="inlineStr"/>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L439" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27280,7 +28644,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K440" t="inlineStr"/>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L440" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27341,7 +28709,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K441" t="inlineStr"/>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L441" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27402,7 +28774,11 @@
           <t>78.209.441-6</t>
         </is>
       </c>
-      <c r="K442" t="inlineStr"/>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L442" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27463,7 +28839,11 @@
           <t>78.209.441-6</t>
         </is>
       </c>
-      <c r="K443" t="inlineStr"/>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L443" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27646,7 +29026,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K446" t="inlineStr"/>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L446" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27768,7 +29152,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K448" t="inlineStr"/>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L448" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27829,7 +29217,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K449" t="inlineStr"/>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L449" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27890,7 +29282,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K450" t="inlineStr"/>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L450" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27951,7 +29347,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K451" t="inlineStr"/>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L451" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28073,7 +29473,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K453" t="inlineStr"/>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L453" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28134,7 +29538,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K454" t="inlineStr"/>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L454" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28195,7 +29603,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K455" t="inlineStr"/>
+      <c r="K455" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L455" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28256,7 +29668,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K456" t="inlineStr"/>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L456" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28317,7 +29733,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K457" t="inlineStr"/>
+      <c r="K457" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L457" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28378,7 +29798,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K458" t="inlineStr"/>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L458" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28500,7 +29924,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K460" t="inlineStr"/>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L460" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28561,7 +29989,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K461" t="inlineStr"/>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L461" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28683,7 +30115,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K463" t="inlineStr"/>
+      <c r="K463" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L463" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28744,7 +30180,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K464" t="inlineStr"/>
+      <c r="K464" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L464" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28805,7 +30245,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K465" t="inlineStr"/>
+      <c r="K465" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L465" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28866,7 +30310,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K466" t="inlineStr"/>
+      <c r="K466" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L466" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28988,7 +30436,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K468" t="inlineStr"/>
+      <c r="K468" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L468" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29049,7 +30501,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K469" t="inlineStr"/>
+      <c r="K469" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L469" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29110,7 +30566,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K470" t="inlineStr"/>
+      <c r="K470" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L470" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29171,7 +30631,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K471" t="inlineStr"/>
+      <c r="K471" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L471" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29232,7 +30696,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K472" t="inlineStr"/>
+      <c r="K472" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L472" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29293,7 +30761,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K473" t="inlineStr"/>
+      <c r="K473" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L473" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29354,7 +30826,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K474" t="inlineStr"/>
+      <c r="K474" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L474" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29476,7 +30952,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K476" t="inlineStr"/>
+      <c r="K476" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L476" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29537,7 +31017,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K477" t="inlineStr"/>
+      <c r="K477" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L477" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29598,7 +31082,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K478" t="inlineStr"/>
+      <c r="K478" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L478" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29720,7 +31208,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K480" t="inlineStr"/>
+      <c r="K480" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L480" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29781,7 +31273,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K481" t="inlineStr"/>
+      <c r="K481" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L481" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29842,7 +31338,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K482" t="inlineStr"/>
+      <c r="K482" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L482" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29903,7 +31403,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K483" t="inlineStr"/>
+      <c r="K483" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L483" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30025,7 +31529,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K485" t="inlineStr"/>
+      <c r="K485" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L485" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30086,7 +31594,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K486" t="inlineStr"/>
+      <c r="K486" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L486" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30147,7 +31659,11 @@
           <t>78.209.441-6</t>
         </is>
       </c>
-      <c r="K487" t="inlineStr"/>
+      <c r="K487" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L487" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30208,7 +31724,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K488" t="inlineStr"/>
+      <c r="K488" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L488" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30330,7 +31850,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K490" t="inlineStr"/>
+      <c r="K490" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L490" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30391,7 +31915,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K491" t="inlineStr"/>
+      <c r="K491" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L491" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30452,7 +31980,11 @@
           <t>78.209.441-6</t>
         </is>
       </c>
-      <c r="K492" t="inlineStr"/>
+      <c r="K492" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L492" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30513,7 +32045,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K493" t="inlineStr"/>
+      <c r="K493" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L493" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30635,7 +32171,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K495" t="inlineStr"/>
+      <c r="K495" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L495" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30757,7 +32297,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K497" t="inlineStr"/>
+      <c r="K497" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L497" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30879,7 +32423,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K499" t="inlineStr"/>
+      <c r="K499" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L499" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30940,7 +32488,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K500" t="inlineStr"/>
+      <c r="K500" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L500" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31123,7 +32675,11 @@
           <t>77.577.274-3</t>
         </is>
       </c>
-      <c r="K503" t="inlineStr"/>
+      <c r="K503" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L503" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31184,7 +32740,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K504" t="inlineStr"/>
+      <c r="K504" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L504" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31306,7 +32866,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K506" t="inlineStr"/>
+      <c r="K506" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L506" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31367,7 +32931,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K507" t="inlineStr"/>
+      <c r="K507" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L507" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31428,7 +32996,11 @@
           <t>78.209.441-6</t>
         </is>
       </c>
-      <c r="K508" t="inlineStr"/>
+      <c r="K508" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L508" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31489,7 +33061,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K509" t="inlineStr"/>
+      <c r="K509" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L509" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31550,7 +33126,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K510" t="inlineStr"/>
+      <c r="K510" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L510" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31672,7 +33252,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K512" t="inlineStr"/>
+      <c r="K512" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L512" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31733,7 +33317,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K513" t="inlineStr"/>
+      <c r="K513" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L513" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31794,7 +33382,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K514" t="inlineStr"/>
+      <c r="K514" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L514" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31855,7 +33447,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K515" t="inlineStr"/>
+      <c r="K515" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L515" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31916,7 +33512,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K516" t="inlineStr"/>
+      <c r="K516" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L516" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31977,7 +33577,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K517" t="inlineStr"/>
+      <c r="K517" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L517" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32038,7 +33642,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K518" t="inlineStr"/>
+      <c r="K518" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L518" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32099,7 +33707,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K519" t="inlineStr"/>
+      <c r="K519" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L519" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32160,7 +33772,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K520" t="inlineStr"/>
+      <c r="K520" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L520" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32221,7 +33837,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K521" t="inlineStr"/>
+      <c r="K521" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L521" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32282,7 +33902,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K522" t="inlineStr"/>
+      <c r="K522" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L522" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32343,7 +33967,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K523" t="inlineStr"/>
+      <c r="K523" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L523" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32404,7 +34032,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K524" t="inlineStr"/>
+      <c r="K524" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L524" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32465,7 +34097,11 @@
           <t>78.209.441-6</t>
         </is>
       </c>
-      <c r="K525" t="inlineStr"/>
+      <c r="K525" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L525" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32526,7 +34162,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K526" t="inlineStr"/>
+      <c r="K526" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L526" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32648,7 +34288,11 @@
           <t>77.393.702-8</t>
         </is>
       </c>
-      <c r="K528" t="inlineStr"/>
+      <c r="K528" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L528" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32709,7 +34353,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K529" t="inlineStr"/>
+      <c r="K529" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L529" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32770,7 +34418,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K530" t="inlineStr"/>
+      <c r="K530" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L530" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32831,7 +34483,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K531" t="inlineStr"/>
+      <c r="K531" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L531" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32892,7 +34548,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K532" t="inlineStr"/>
+      <c r="K532" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L532" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32953,7 +34613,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K533" t="inlineStr"/>
+      <c r="K533" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L533" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33136,7 +34800,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K536" t="inlineStr"/>
+      <c r="K536" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L536" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33197,7 +34865,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K537" t="inlineStr"/>
+      <c r="K537" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L537" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33258,7 +34930,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K538" t="inlineStr"/>
+      <c r="K538" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L538" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33441,7 +35117,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K541" t="inlineStr"/>
+      <c r="K541" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L541" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33502,7 +35182,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K542" t="inlineStr"/>
+      <c r="K542" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L542" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33563,7 +35247,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K543" t="inlineStr"/>
+      <c r="K543" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L543" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33624,7 +35312,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K544" t="inlineStr"/>
+      <c r="K544" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L544" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33685,7 +35377,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K545" t="inlineStr"/>
+      <c r="K545" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L545" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33746,7 +35442,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K546" t="inlineStr"/>
+      <c r="K546" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L546" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33807,7 +35507,11 @@
           <t>78.209.499-8</t>
         </is>
       </c>
-      <c r="K547" t="inlineStr"/>
+      <c r="K547" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L547" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33929,7 +35633,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K549" t="inlineStr"/>
+      <c r="K549" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L549" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33990,7 +35698,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K550" t="inlineStr"/>
+      <c r="K550" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L550" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34051,7 +35763,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K551" t="inlineStr"/>
+      <c r="K551" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L551" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34112,7 +35828,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K552" t="inlineStr"/>
+      <c r="K552" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L552" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34173,7 +35893,11 @@
           <t>76.102.347-0</t>
         </is>
       </c>
-      <c r="K553" t="inlineStr"/>
+      <c r="K553" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L553" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34234,7 +35958,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K554" t="inlineStr"/>
+      <c r="K554" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L554" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34295,7 +36023,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K555" t="inlineStr"/>
+      <c r="K555" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L555" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34356,7 +36088,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K556" t="inlineStr"/>
+      <c r="K556" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L556" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34417,7 +36153,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K557" t="inlineStr"/>
+      <c r="K557" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L557" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34604,7 +36344,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K560" t="inlineStr"/>
+      <c r="K560" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L560" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34665,7 +36409,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K561" t="inlineStr"/>
+      <c r="K561" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L561" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34726,7 +36474,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K562" t="inlineStr"/>
+      <c r="K562" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L562" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34787,7 +36539,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K563" t="inlineStr"/>
+      <c r="K563" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L563" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34848,7 +36604,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K564" t="inlineStr"/>
+      <c r="K564" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L564" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34909,7 +36669,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K565" t="inlineStr"/>
+      <c r="K565" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L565" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34970,7 +36734,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K566" t="inlineStr"/>
+      <c r="K566" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L566" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35092,7 +36860,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K568" t="inlineStr"/>
+      <c r="K568" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L568" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35153,7 +36925,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K569" t="inlineStr"/>
+      <c r="K569" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L569" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35214,7 +36990,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K570" t="inlineStr"/>
+      <c r="K570" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L570" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35275,7 +37055,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K571" t="inlineStr"/>
+      <c r="K571" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L571" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35336,7 +37120,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K572" t="inlineStr"/>
+      <c r="K572" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L572" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35397,7 +37185,11 @@
           <t>78.209.441-6</t>
         </is>
       </c>
-      <c r="K573" t="inlineStr"/>
+      <c r="K573" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L573" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35458,7 +37250,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K574" t="inlineStr"/>
+      <c r="K574" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L574" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35519,7 +37315,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K575" t="inlineStr"/>
+      <c r="K575" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L575" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35702,7 +37502,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K578" t="inlineStr"/>
+      <c r="K578" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L578" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35824,7 +37628,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K580" t="inlineStr"/>
+      <c r="K580" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L580" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35946,7 +37754,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K582" t="inlineStr"/>
+      <c r="K582" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L582" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36007,7 +37819,11 @@
           <t>78.212.867-1</t>
         </is>
       </c>
-      <c r="K583" t="inlineStr"/>
+      <c r="K583" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L583" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36129,7 +37945,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K585" t="inlineStr"/>
+      <c r="K585" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L585" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36190,7 +38010,11 @@
           <t>76.556.184-1</t>
         </is>
       </c>
-      <c r="K586" t="inlineStr"/>
+      <c r="K586" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L586" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36312,7 +38136,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K588" t="inlineStr"/>
+      <c r="K588" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L588" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36373,7 +38201,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K589" t="inlineStr"/>
+      <c r="K589" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L589" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36434,7 +38266,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K590" t="inlineStr"/>
+      <c r="K590" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L590" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36560,7 +38396,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K592" t="inlineStr"/>
+      <c r="K592" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L592" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36621,7 +38461,11 @@
           <t>78.199.695-5</t>
         </is>
       </c>
-      <c r="K593" t="inlineStr"/>
+      <c r="K593" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L593" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36682,7 +38526,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K594" t="inlineStr"/>
+      <c r="K594" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L594" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36743,7 +38591,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K595" t="inlineStr"/>
+      <c r="K595" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L595" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36926,7 +38778,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K598" t="inlineStr"/>
+      <c r="K598" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L598" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36987,7 +38843,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K599" t="inlineStr"/>
+      <c r="K599" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L599" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37048,7 +38908,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K600" t="inlineStr"/>
+      <c r="K600" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L600" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37109,7 +38973,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K601" t="inlineStr"/>
+      <c r="K601" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L601" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37170,7 +39038,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K602" t="inlineStr"/>
+      <c r="K602" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L602" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37231,7 +39103,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K603" t="inlineStr"/>
+      <c r="K603" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L603" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37292,7 +39168,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K604" t="inlineStr"/>
+      <c r="K604" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L604" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37353,7 +39233,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K605" t="inlineStr"/>
+      <c r="K605" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L605" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37414,7 +39298,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K606" t="inlineStr"/>
+      <c r="K606" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L606" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37475,7 +39363,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K607" t="inlineStr"/>
+      <c r="K607" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L607" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37536,7 +39428,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K608" t="inlineStr"/>
+      <c r="K608" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L608" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37597,7 +39493,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K609" t="inlineStr"/>
+      <c r="K609" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L609" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37719,7 +39619,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K611" t="inlineStr"/>
+      <c r="K611" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L611" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37780,7 +39684,11 @@
           <t>77.823.479-3</t>
         </is>
       </c>
-      <c r="K612" t="inlineStr"/>
+      <c r="K612" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L612" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37841,7 +39749,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K613" t="inlineStr"/>
+      <c r="K613" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L613" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37902,7 +39814,11 @@
           <t>78.212.867-1</t>
         </is>
       </c>
-      <c r="K614" t="inlineStr"/>
+      <c r="K614" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L614" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37963,7 +39879,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K615" t="inlineStr"/>
+      <c r="K615" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L615" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38024,7 +39944,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K616" t="inlineStr"/>
+      <c r="K616" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L616" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38085,7 +40009,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K617" t="inlineStr"/>
+      <c r="K617" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L617" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38146,7 +40074,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K618" t="inlineStr"/>
+      <c r="K618" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L618" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38207,7 +40139,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K619" t="inlineStr"/>
+      <c r="K619" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L619" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38268,7 +40204,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K620" t="inlineStr"/>
+      <c r="K620" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L620" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38390,7 +40330,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K622" t="inlineStr"/>
+      <c r="K622" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L622" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38512,7 +40456,11 @@
           <t>78.212.867-1</t>
         </is>
       </c>
-      <c r="K624" t="inlineStr"/>
+      <c r="K624" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L624" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38573,7 +40521,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K625" t="inlineStr"/>
+      <c r="K625" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L625" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38634,7 +40586,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K626" t="inlineStr"/>
+      <c r="K626" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L626" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38756,7 +40712,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K628" t="inlineStr"/>
+      <c r="K628" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L628" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38817,7 +40777,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K629" t="inlineStr"/>
+      <c r="K629" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L629" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38878,7 +40842,11 @@
           <t>77.935.401-6</t>
         </is>
       </c>
-      <c r="K630" t="inlineStr"/>
+      <c r="K630" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L630" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38939,7 +40907,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K631" t="inlineStr"/>
+      <c r="K631" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L631" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39000,7 +40972,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K632" t="inlineStr"/>
+      <c r="K632" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L632" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39061,7 +41037,11 @@
           <t>78.209.441-6</t>
         </is>
       </c>
-      <c r="K633" t="inlineStr"/>
+      <c r="K633" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L633" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39122,7 +41102,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K634" t="inlineStr"/>
+      <c r="K634" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L634" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39183,7 +41167,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K635" t="inlineStr"/>
+      <c r="K635" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L635" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39244,7 +41232,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K636" t="inlineStr"/>
+      <c r="K636" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L636" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39366,7 +41358,11 @@
           <t>78.212.867-1</t>
         </is>
       </c>
-      <c r="K638" t="inlineStr"/>
+      <c r="K638" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L638" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39427,7 +41423,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K639" t="inlineStr"/>
+      <c r="K639" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L639" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39488,7 +41488,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K640" t="inlineStr"/>
+      <c r="K640" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L640" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39549,7 +41553,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K641" t="inlineStr"/>
+      <c r="K641" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L641" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39610,7 +41618,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K642" t="inlineStr"/>
+      <c r="K642" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L642" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39671,7 +41683,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K643" t="inlineStr"/>
+      <c r="K643" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L643" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39732,7 +41748,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K644" t="inlineStr"/>
+      <c r="K644" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L644" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39793,7 +41813,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K645" t="inlineStr"/>
+      <c r="K645" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L645" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39854,7 +41878,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K646" t="inlineStr"/>
+      <c r="K646" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L646" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39915,7 +41943,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K647" t="inlineStr"/>
+      <c r="K647" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L647" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39976,7 +42008,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K648" t="inlineStr"/>
+      <c r="K648" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L648" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40037,7 +42073,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K649" t="inlineStr"/>
+      <c r="K649" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L649" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40098,7 +42138,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K650" t="inlineStr"/>
+      <c r="K650" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L650" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40220,7 +42264,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K652" t="inlineStr"/>
+      <c r="K652" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L652" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40281,7 +42329,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K653" t="inlineStr"/>
+      <c r="K653" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L653" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40403,7 +42455,11 @@
           <t>76.556.184-1</t>
         </is>
       </c>
-      <c r="K655" t="inlineStr"/>
+      <c r="K655" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L655" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40464,7 +42520,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K656" t="inlineStr"/>
+      <c r="K656" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L656" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40525,7 +42585,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K657" t="inlineStr"/>
+      <c r="K657" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L657" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40586,7 +42650,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K658" t="inlineStr"/>
+      <c r="K658" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L658" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40647,7 +42715,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K659" t="inlineStr"/>
+      <c r="K659" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L659" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40708,7 +42780,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K660" t="inlineStr"/>
+      <c r="K660" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L660" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40769,7 +42845,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K661" t="inlineStr"/>
+      <c r="K661" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L661" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40830,7 +42910,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K662" t="inlineStr"/>
+      <c r="K662" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L662" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40891,7 +42975,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K663" t="inlineStr"/>
+      <c r="K663" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L663" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40952,7 +43040,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K664" t="inlineStr"/>
+      <c r="K664" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L664" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41013,7 +43105,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K665" t="inlineStr"/>
+      <c r="K665" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L665" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41196,7 +43292,11 @@
           <t>78.209.441-6</t>
         </is>
       </c>
-      <c r="K668" t="inlineStr"/>
+      <c r="K668" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L668" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41257,7 +43357,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K669" t="inlineStr"/>
+      <c r="K669" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L669" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41379,7 +43483,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K671" t="inlineStr"/>
+      <c r="K671" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L671" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41440,7 +43548,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K672" t="inlineStr"/>
+      <c r="K672" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L672" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41501,7 +43613,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K673" t="inlineStr"/>
+      <c r="K673" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L673" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41562,7 +43678,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K674" t="inlineStr"/>
+      <c r="K674" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L674" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41684,7 +43804,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K676" t="inlineStr"/>
+      <c r="K676" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L676" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41806,7 +43930,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K678" t="inlineStr"/>
+      <c r="K678" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L678" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41867,7 +43995,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K679" t="inlineStr"/>
+      <c r="K679" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L679" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41928,7 +44060,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K680" t="inlineStr"/>
+      <c r="K680" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L680" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41989,7 +44125,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K681" t="inlineStr"/>
+      <c r="K681" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L681" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42050,7 +44190,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K682" t="inlineStr"/>
+      <c r="K682" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L682" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42111,7 +44255,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K683" t="inlineStr"/>
+      <c r="K683" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L683" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42172,7 +44320,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K684" t="inlineStr"/>
+      <c r="K684" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L684" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42233,7 +44385,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K685" t="inlineStr"/>
+      <c r="K685" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L685" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42294,7 +44450,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K686" t="inlineStr"/>
+      <c r="K686" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L686" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42355,7 +44515,11 @@
           <t>78.199.695-5</t>
         </is>
       </c>
-      <c r="K687" t="inlineStr"/>
+      <c r="K687" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L687" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42416,7 +44580,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K688" t="inlineStr"/>
+      <c r="K688" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L688" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42477,7 +44645,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K689" t="inlineStr"/>
+      <c r="K689" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L689" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42538,7 +44710,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K690" t="inlineStr"/>
+      <c r="K690" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L690" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42599,7 +44775,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K691" t="inlineStr"/>
+      <c r="K691" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L691" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42660,7 +44840,11 @@
           <t>76.556.184-1</t>
         </is>
       </c>
-      <c r="K692" t="inlineStr"/>
+      <c r="K692" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L692" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42782,7 +44966,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K694" t="inlineStr"/>
+      <c r="K694" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L694" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42843,7 +45031,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K695" t="inlineStr"/>
+      <c r="K695" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L695" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42904,7 +45096,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K696" t="inlineStr"/>
+      <c r="K696" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L696" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42965,7 +45161,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K697" t="inlineStr"/>
+      <c r="K697" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L697" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43026,7 +45226,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K698" t="inlineStr"/>
+      <c r="K698" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L698" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43087,7 +45291,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K699" t="inlineStr"/>
+      <c r="K699" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L699" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43148,7 +45356,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K700" t="inlineStr"/>
+      <c r="K700" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L700" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43270,7 +45482,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K702" t="inlineStr"/>
+      <c r="K702" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L702" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43453,7 +45669,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K705" t="inlineStr"/>
+      <c r="K705" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L705" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43514,7 +45734,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K706" t="inlineStr"/>
+      <c r="K706" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L706" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43575,7 +45799,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K707" t="inlineStr"/>
+      <c r="K707" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L707" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43636,7 +45864,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K708" t="inlineStr"/>
+      <c r="K708" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L708" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43697,7 +45929,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K709" t="inlineStr"/>
+      <c r="K709" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L709" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43758,7 +45994,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K710" t="inlineStr"/>
+      <c r="K710" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L710" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43819,7 +46059,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K711" t="inlineStr"/>
+      <c r="K711" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L711" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43880,7 +46124,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K712" t="inlineStr"/>
+      <c r="K712" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L712" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43941,7 +46189,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K713" t="inlineStr"/>
+      <c r="K713" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L713" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44063,7 +46315,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K715" t="inlineStr"/>
+      <c r="K715" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L715" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44124,7 +46380,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K716" t="inlineStr"/>
+      <c r="K716" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L716" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44185,7 +46445,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K717" t="inlineStr"/>
+      <c r="K717" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L717" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44246,7 +46510,11 @@
           <t>78.209.499-8</t>
         </is>
       </c>
-      <c r="K718" t="inlineStr"/>
+      <c r="K718" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L718" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44307,7 +46575,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K719" t="inlineStr"/>
+      <c r="K719" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L719" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44368,7 +46640,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K720" t="inlineStr"/>
+      <c r="K720" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L720" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44429,7 +46705,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K721" t="inlineStr"/>
+      <c r="K721" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L721" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44490,7 +46770,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K722" t="inlineStr"/>
+      <c r="K722" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L722" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44551,7 +46835,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K723" t="inlineStr"/>
+      <c r="K723" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L723" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44612,7 +46900,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K724" t="inlineStr"/>
+      <c r="K724" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L724" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44673,7 +46965,11 @@
           <t>76.556.184-1</t>
         </is>
       </c>
-      <c r="K725" t="inlineStr"/>
+      <c r="K725" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L725" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44734,7 +47030,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K726" t="inlineStr"/>
+      <c r="K726" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L726" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44917,7 +47217,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K729" t="inlineStr"/>
+      <c r="K729" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L729" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45039,7 +47343,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K731" t="inlineStr"/>
+      <c r="K731" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L731" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45100,7 +47408,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K732" t="inlineStr"/>
+      <c r="K732" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L732" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45161,7 +47473,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K733" t="inlineStr"/>
+      <c r="K733" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L733" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45222,7 +47538,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K734" t="inlineStr"/>
+      <c r="K734" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L734" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45283,7 +47603,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K735" t="inlineStr"/>
+      <c r="K735" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L735" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45405,7 +47729,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K737" t="inlineStr"/>
+      <c r="K737" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L737" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45466,7 +47794,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K738" t="inlineStr"/>
+      <c r="K738" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L738" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45588,7 +47920,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K740" t="inlineStr"/>
+      <c r="K740" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L740" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45649,7 +47985,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K741" t="inlineStr"/>
+      <c r="K741" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L741" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45710,7 +48050,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K742" t="inlineStr"/>
+      <c r="K742" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L742" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45771,7 +48115,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K743" t="inlineStr"/>
+      <c r="K743" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L743" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45893,7 +48241,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K745" t="inlineStr"/>
+      <c r="K745" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L745" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45954,7 +48306,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K746" t="inlineStr"/>
+      <c r="K746" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L746" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46015,7 +48371,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K747" t="inlineStr"/>
+      <c r="K747" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L747" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46076,7 +48436,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K748" t="inlineStr"/>
+      <c r="K748" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L748" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46137,7 +48501,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K749" t="inlineStr"/>
+      <c r="K749" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L749" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46198,7 +48566,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K750" t="inlineStr"/>
+      <c r="K750" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L750" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46385,7 +48757,11 @@
           <t>77.404.653-4</t>
         </is>
       </c>
-      <c r="K753" t="inlineStr"/>
+      <c r="K753" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L753" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46446,7 +48822,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K754" t="inlineStr"/>
+      <c r="K754" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L754" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46507,7 +48887,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K755" t="inlineStr"/>
+      <c r="K755" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L755" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46568,7 +48952,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K756" t="inlineStr"/>
+      <c r="K756" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L756" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46629,7 +49017,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K757" t="inlineStr"/>
+      <c r="K757" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L757" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46690,7 +49082,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K758" t="inlineStr"/>
+      <c r="K758" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L758" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46751,7 +49147,11 @@
           <t>77.649.678-2</t>
         </is>
       </c>
-      <c r="K759" t="inlineStr"/>
+      <c r="K759" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L759" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46812,7 +49212,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K760" t="inlineStr"/>
+      <c r="K760" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L760" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46873,7 +49277,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K761" t="inlineStr"/>
+      <c r="K761" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L761" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46934,7 +49342,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K762" t="inlineStr"/>
+      <c r="K762" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L762" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47056,7 +49468,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K764" t="inlineStr"/>
+      <c r="K764" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L764" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47117,7 +49533,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K765" t="inlineStr"/>
+      <c r="K765" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L765" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47178,7 +49598,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K766" t="inlineStr"/>
+      <c r="K766" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L766" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47239,7 +49663,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K767" t="inlineStr"/>
+      <c r="K767" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L767" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47300,7 +49728,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K768" t="inlineStr"/>
+      <c r="K768" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L768" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47361,7 +49793,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K769" t="inlineStr"/>
+      <c r="K769" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L769" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47422,7 +49858,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K770" t="inlineStr"/>
+      <c r="K770" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L770" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47483,7 +49923,11 @@
           <t>76.556.184-1</t>
         </is>
       </c>
-      <c r="K771" t="inlineStr"/>
+      <c r="K771" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L771" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47605,7 +50049,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K773" t="inlineStr"/>
+      <c r="K773" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L773" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47666,7 +50114,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K774" t="inlineStr"/>
+      <c r="K774" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L774" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47727,7 +50179,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K775" t="inlineStr"/>
+      <c r="K775" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L775" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/articulos-de-aseo-e-higiene/coquimbo.xlsx
+++ b/docs/oc-regiones/articulos-de-aseo-e-higiene/coquimbo.xlsx
@@ -2667,7 +2667,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3431,7 +3435,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4390,7 +4398,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5422,7 +5434,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5483,7 +5499,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9774,7 +9794,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10095,7 +10119,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10867,7 +10895,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11123,7 +11155,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11505,7 +11541,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11692,7 +11732,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16154,7 +16198,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr"/>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L246" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18218,7 +18266,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K278" t="inlineStr"/>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L278" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19945,7 +19997,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K305" t="inlineStr"/>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L305" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21229,7 +21285,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K325" t="inlineStr"/>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L325" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26454,7 +26514,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K406" t="inlineStr"/>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L406" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28258,7 +28322,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K434" t="inlineStr"/>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L434" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28904,7 +28972,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K444" t="inlineStr"/>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L444" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29091,7 +29163,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K447" t="inlineStr"/>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L447" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29412,7 +29488,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K452" t="inlineStr"/>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L452" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29863,7 +29943,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K459" t="inlineStr"/>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L459" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30054,7 +30138,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K462" t="inlineStr"/>
+      <c r="K462" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L462" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30891,7 +30979,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K475" t="inlineStr"/>
+      <c r="K475" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L475" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31147,7 +31239,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K479" t="inlineStr"/>
+      <c r="K479" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L479" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31789,7 +31885,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K489" t="inlineStr"/>
+      <c r="K489" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L489" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32110,7 +32210,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K494" t="inlineStr"/>
+      <c r="K494" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L494" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32236,7 +32340,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K496" t="inlineStr"/>
+      <c r="K496" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L496" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32553,7 +32661,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K501" t="inlineStr"/>
+      <c r="K501" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L501" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32805,7 +32917,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K505" t="inlineStr"/>
+      <c r="K505" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L505" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34678,7 +34794,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K534" t="inlineStr"/>
+      <c r="K534" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L534" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34739,7 +34859,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K535" t="inlineStr"/>
+      <c r="K535" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L535" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35056,7 +35180,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K540" t="inlineStr"/>
+      <c r="K540" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L540" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36218,7 +36346,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K558" t="inlineStr"/>
+      <c r="K558" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L558" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36799,7 +36931,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K567" t="inlineStr"/>
+      <c r="K567" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L567" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37380,7 +37516,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K576" t="inlineStr"/>
+      <c r="K576" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L576" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37441,7 +37581,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K577" t="inlineStr"/>
+      <c r="K577" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L577" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37567,7 +37711,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K579" t="inlineStr"/>
+      <c r="K579" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L579" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37884,7 +38032,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K584" t="inlineStr"/>
+      <c r="K584" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L584" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38075,7 +38227,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K587" t="inlineStr"/>
+      <c r="K587" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L587" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38656,7 +38812,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K596" t="inlineStr"/>
+      <c r="K596" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L596" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38717,7 +38877,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K597" t="inlineStr"/>
+      <c r="K597" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L597" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40269,7 +40433,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K621" t="inlineStr"/>
+      <c r="K621" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L621" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40395,7 +40563,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K623" t="inlineStr"/>
+      <c r="K623" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L623" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40651,7 +40823,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K627" t="inlineStr"/>
+      <c r="K627" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L627" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42203,7 +42379,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K651" t="inlineStr"/>
+      <c r="K651" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L651" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42394,7 +42574,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K654" t="inlineStr"/>
+      <c r="K654" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L654" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43170,7 +43354,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K666" t="inlineStr"/>
+      <c r="K666" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L666" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43422,7 +43610,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K670" t="inlineStr"/>
+      <c r="K670" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L670" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43743,7 +43935,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K675" t="inlineStr"/>
+      <c r="K675" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L675" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44905,7 +45101,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K693" t="inlineStr"/>
+      <c r="K693" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L693" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45547,7 +45747,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K703" t="inlineStr"/>
+      <c r="K703" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L703" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47156,7 +47360,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K728" t="inlineStr"/>
+      <c r="K728" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L728" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47668,7 +47876,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K736" t="inlineStr"/>
+      <c r="K736" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L736" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47859,7 +48071,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K739" t="inlineStr"/>
+      <c r="K739" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L739" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48180,7 +48396,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K744" t="inlineStr"/>
+      <c r="K744" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L744" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49407,7 +49627,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K763" t="inlineStr"/>
+      <c r="K763" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L763" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/articulos-de-aseo-e-higiene/coquimbo.xlsx
+++ b/docs/oc-regiones/articulos-de-aseo-e-higiene/coquimbo.xlsx
@@ -51805,7 +51805,7 @@
       </c>
       <c r="E797" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F797" t="inlineStr">
@@ -52390,7 +52390,7 @@
       </c>
       <c r="E806" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F806" t="inlineStr">
